--- a/simulations/correction_peat_market/AS_marché/AS_marché_hobby/AS_resume_hobby.xlsx
+++ b/simulations/correction_peat_market/AS_marché/AS_marché_hobby/AS_resume_hobby.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\hravoaha\Desktop\Thèse\Thèse 2023\Objectif 2\biowaste_optim\simulations\correction_peat_market\AS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\hravoaha\Desktop\Thèse\Thèse 2023\Objectif 2\biowaste_optim\simulations\correction_peat_market\AS_marché\AS_marché_hobby\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F59E6814-A43B-41AA-B598-685003406BE2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A426642-21AB-4AB9-9F9A-150770E766E0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="inv" sheetId="1" r:id="rId1"/>
@@ -23,6 +23,11 @@
     <externalReference r:id="rId6"/>
     <externalReference r:id="rId7"/>
     <externalReference r:id="rId8"/>
+    <externalReference r:id="rId9"/>
+    <externalReference r:id="rId10"/>
+    <externalReference r:id="rId11"/>
+    <externalReference r:id="rId12"/>
+    <externalReference r:id="rId13"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
@@ -177,10 +182,10 @@
           <c:invertIfNegative val="0"/>
           <c:val>
             <c:numRef>
-              <c:f>inv!$A$4:$A$30</c:f>
+              <c:f>inv!$A$4:$A$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="27"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="1">
                   <c:v>0</c:v>
                 </c:pt>
@@ -188,18 +193,6 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="25">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -234,7 +227,7 @@
           <c:invertIfNegative val="0"/>
           <c:val>
             <c:numRef>
-              <c:f>inv!$B$4:$B$30</c:f>
+              <c:f>inv!$B$4:$B$14</c:f>
             </c:numRef>
           </c:val>
           <c:extLst>
@@ -269,21 +262,21 @@
           <c:invertIfNegative val="0"/>
           <c:val>
             <c:numRef>
-              <c:f>inv!$C$4:$C$30</c:f>
+              <c:f>inv!$C$4:$C$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="27"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>26.550000000000004</c:v>
+                  <c:v>6.5</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>6.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>8.86</c:v>
+                  <c:v>6.5</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>26.550000000000004</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0</c:v>
@@ -292,48 +285,12 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>26.550000000000004</c:v>
+                  <c:v>1.29</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>1.29</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.29</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>26.550000000000004</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>26.550000000000004</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>1.29</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>1.29</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>26.550000000000004</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>6.5</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>8.86</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>26.550000000000004</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>1.29</c:v>
-                </c:pt>
-                <c:pt idx="26">
                   <c:v>1.29</c:v>
                 </c:pt>
               </c:numCache>
@@ -371,12 +328,12 @@
           <c:invertIfNegative val="0"/>
           <c:val>
             <c:numRef>
-              <c:f>inv!$D$4:$D$30</c:f>
+              <c:f>inv!$D$4:$D$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="27"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>32.229999999999997</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
@@ -400,42 +357,6 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>26.729999999999997</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="26">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -473,10 +394,10 @@
           <c:invertIfNegative val="0"/>
           <c:val>
             <c:numRef>
-              <c:f>inv!$E$4:$E$30</c:f>
+              <c:f>inv!$E$4:$E$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="27"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -502,42 +423,6 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="26">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -575,10 +460,10 @@
           <c:invertIfNegative val="0"/>
           <c:val>
             <c:numRef>
-              <c:f>inv!$F$4:$F$30</c:f>
+              <c:f>inv!$F$4:$F$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="27"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -589,7 +474,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>73.459999999999994</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0</c:v>
@@ -598,48 +483,12 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>73.459999999999994</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>73.459999999999994</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>73.459999999999994</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>46.73</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>73.459999999999994</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="26">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -679,12 +528,12 @@
           <c:invertIfNegative val="0"/>
           <c:val>
             <c:numRef>
-              <c:f>inv!$G$4:$G$30</c:f>
+              <c:f>inv!$G$4:$G$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="27"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>41.23</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
@@ -708,42 +557,6 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="26">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -783,18 +596,18 @@
           <c:invertIfNegative val="0"/>
           <c:val>
             <c:numRef>
-              <c:f>inv!$H$4:$H$30</c:f>
+              <c:f>inv!$H$4:$H$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="27"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>93.51</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>93.51</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>93.51</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>0</c:v>
@@ -812,42 +625,6 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="26">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -887,10 +664,10 @@
           <c:invertIfNegative val="0"/>
           <c:val>
             <c:numRef>
-              <c:f>inv!$I$4:$I$30</c:f>
+              <c:f>inv!$I$4:$I$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="27"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -916,42 +693,6 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="26">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -991,21 +732,21 @@
           <c:invertIfNegative val="0"/>
           <c:val>
             <c:numRef>
-              <c:f>inv!$J$4:$J$30</c:f>
+              <c:f>inv!$J$4:$J$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="27"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>93.51</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>91.15</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>100</c:v>
@@ -1014,48 +755,12 @@
                   <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0</c:v>
+                  <c:v>98.71</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>98.71</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>98.71</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>98.71</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>98.71</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>93.51</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>91.15</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>98.71</c:v>
-                </c:pt>
-                <c:pt idx="26">
                   <c:v>98.71</c:v>
                 </c:pt>
               </c:numCache>
@@ -1350,10 +1055,10 @@
           <c:invertIfNegative val="0"/>
           <c:val>
             <c:numRef>
-              <c:f>ss_inv!$A$3:$A$29</c:f>
+              <c:f>ss_inv!$A$3:$A$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="27"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="1">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1361,18 +1066,6 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="25">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -1410,72 +1103,36 @@
           <c:invertIfNegative val="0"/>
           <c:val>
             <c:numRef>
-              <c:f>ss_inv!$B$3:$B$29</c:f>
+              <c:f>ss_inv!$B$3:$B$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="27"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>26.550000000000004</c:v>
+                  <c:v>11.95</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>13.280000000000001</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>8.86</c:v>
+                  <c:v>14.61</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>26.550000000000004</c:v>
+                  <c:v>11.95</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>13.280000000000001</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>8.86</c:v>
+                  <c:v>14.61</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>26.550000000000004</c:v>
+                  <c:v>11.95</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>13.280000000000001</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>8.86</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>26.550000000000004</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>13.280000000000001</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>8.86</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>26.550000000000004</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>13.280000000000001</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>8.86</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>26.550000000000004</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>13.280000000000001</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>8.86</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>26.550000000000004</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>13.280000000000001</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>8.86</c:v>
+                  <c:v>14.61</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1512,18 +1169,18 @@
           <c:invertIfNegative val="0"/>
           <c:val>
             <c:numRef>
-              <c:f>ss_inv!$C$3:$C$29</c:f>
+              <c:f>ss_inv!$C$3:$C$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="27"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>32.229999999999997</c:v>
+                  <c:v>14.5</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>16.11</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>6.95</c:v>
+                  <c:v>17.72</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>0</c:v>
@@ -1532,7 +1189,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>3.41</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0</c:v>
@@ -1541,43 +1198,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>3.41</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>3.41</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>3.41</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>26.729999999999997</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>6.6999999999999993</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>3.41</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>3.41</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1614,10 +1235,10 @@
           <c:invertIfNegative val="0"/>
           <c:val>
             <c:numRef>
-              <c:f>ss_inv!$D$3:$D$29</c:f>
+              <c:f>ss_inv!$D$3:$D$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="27"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1625,61 +1246,25 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>32.25</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>73.459999999999994</c:v>
+                  <c:v>88.06</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>86.73</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>62.34</c:v>
+                  <c:v>85.4</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>73.459999999999994</c:v>
+                  <c:v>88.06</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>86.73</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>62.34</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>73.459999999999994</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>86.73</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>62.34</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>73.459999999999994</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>86.73</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>62.34</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>46.73</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>80.03</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>62.34</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>73.459999999999994</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>86.73</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>62.34</c:v>
+                  <c:v>85.4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1716,18 +1301,18 @@
           <c:invertIfNegative val="0"/>
           <c:val>
             <c:numRef>
-              <c:f>ss_inv!$E$3:$E$29</c:f>
+              <c:f>ss_inv!$E$3:$E$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="27"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>41.23</c:v>
+                  <c:v>73.55</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>70.62</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>51.95</c:v>
+                  <c:v>67.680000000000007</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>0</c:v>
@@ -1736,7 +1321,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>25.4</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0</c:v>
@@ -1745,43 +1330,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>25.4</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>25.4</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>25.4</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>25.4</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>25.4</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3092,16 +2641,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>247648</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>800100</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>130175</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>95250</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>130175</xdr:rowOff>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>63500</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -3133,16 +2682,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>693737</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>430212</xdr:colOff>
+      <xdr:row>2</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>476250</xdr:colOff>
+      <xdr:colOff>457200</xdr:colOff>
       <xdr:row>31</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:rowOff>139700</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -3175,7 +2724,9 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="results"/>
+      <sheetName val="Feuil2"/>
       <sheetName val="Feuil1"/>
+      <sheetName val="Feuil3"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
@@ -3210,31 +2761,7 @@
         </row>
         <row r="3">
           <cell r="AQ3" t="str">
-            <v>minCO2</v>
-          </cell>
-          <cell r="AR3">
-            <v>6.5</v>
-          </cell>
-          <cell r="AS3">
-            <v>0</v>
-          </cell>
-          <cell r="AT3">
-            <v>0</v>
-          </cell>
-          <cell r="AU3">
-            <v>0</v>
-          </cell>
-          <cell r="AV3">
-            <v>0</v>
-          </cell>
-          <cell r="AW3">
-            <v>0</v>
-          </cell>
-          <cell r="AX3">
-            <v>0</v>
-          </cell>
-          <cell r="AY3">
-            <v>93.51</v>
+            <v>minCC</v>
           </cell>
           <cell r="AZ3">
             <v>100.01</v>
@@ -3244,30 +2771,6 @@
           <cell r="AQ4" t="str">
             <v>minEQ</v>
           </cell>
-          <cell r="AR4">
-            <v>0</v>
-          </cell>
-          <cell r="AS4">
-            <v>0</v>
-          </cell>
-          <cell r="AT4">
-            <v>0</v>
-          </cell>
-          <cell r="AU4">
-            <v>0</v>
-          </cell>
-          <cell r="AV4">
-            <v>0</v>
-          </cell>
-          <cell r="AW4">
-            <v>0</v>
-          </cell>
-          <cell r="AX4">
-            <v>0</v>
-          </cell>
-          <cell r="AY4">
-            <v>100</v>
-          </cell>
           <cell r="AZ4">
             <v>100</v>
           </cell>
@@ -3276,164 +2779,126 @@
           <cell r="AQ5" t="str">
             <v>minHH</v>
           </cell>
-          <cell r="AR5">
-            <v>1.29</v>
-          </cell>
-          <cell r="AS5">
-            <v>0</v>
-          </cell>
-          <cell r="AT5">
-            <v>0</v>
-          </cell>
-          <cell r="AU5">
-            <v>0</v>
-          </cell>
-          <cell r="AV5">
-            <v>0</v>
-          </cell>
-          <cell r="AW5">
-            <v>0</v>
-          </cell>
-          <cell r="AX5">
-            <v>0</v>
-          </cell>
-          <cell r="AY5">
-            <v>98.71</v>
-          </cell>
           <cell r="AZ5">
-            <v>100</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="AQ6" t="str">
-            <v>minEQ&amp;HH</v>
-          </cell>
-          <cell r="AR6">
-            <v>0</v>
-          </cell>
-          <cell r="AS6">
-            <v>0</v>
-          </cell>
-          <cell r="AT6">
-            <v>0</v>
-          </cell>
-          <cell r="AU6">
-            <v>0</v>
-          </cell>
-          <cell r="AV6">
-            <v>0</v>
-          </cell>
-          <cell r="AW6">
-            <v>0</v>
-          </cell>
-          <cell r="AX6">
-            <v>0</v>
-          </cell>
-          <cell r="AY6">
-            <v>100</v>
-          </cell>
-          <cell r="AZ6">
-            <v>100</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="AQ7" t="str">
-            <v>minCO2&amp;EQ</v>
-          </cell>
-          <cell r="AR7">
-            <v>1.29</v>
-          </cell>
-          <cell r="AS7">
-            <v>0</v>
-          </cell>
-          <cell r="AT7">
-            <v>0</v>
-          </cell>
-          <cell r="AU7">
-            <v>0</v>
-          </cell>
-          <cell r="AV7">
-            <v>0</v>
-          </cell>
-          <cell r="AW7">
-            <v>0</v>
-          </cell>
-          <cell r="AX7">
-            <v>0</v>
-          </cell>
-          <cell r="AY7">
-            <v>98.71</v>
-          </cell>
-          <cell r="AZ7">
-            <v>100</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="AQ8" t="str">
-            <v>minCO2&amp;HH</v>
-          </cell>
-          <cell r="AR8">
-            <v>6.5</v>
-          </cell>
-          <cell r="AS8">
-            <v>0</v>
-          </cell>
-          <cell r="AT8">
-            <v>0</v>
-          </cell>
-          <cell r="AU8">
-            <v>0</v>
-          </cell>
-          <cell r="AV8">
-            <v>0</v>
-          </cell>
-          <cell r="AW8">
-            <v>0</v>
-          </cell>
-          <cell r="AX8">
-            <v>0</v>
-          </cell>
-          <cell r="AY8">
-            <v>93.51</v>
-          </cell>
-          <cell r="AZ8">
-            <v>100.01</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="AQ9" t="str">
-            <v>minCO2&amp;EQ&amp;HH</v>
-          </cell>
-          <cell r="AR9">
-            <v>1.29</v>
-          </cell>
-          <cell r="AS9">
-            <v>0</v>
-          </cell>
-          <cell r="AT9">
-            <v>0</v>
-          </cell>
-          <cell r="AU9">
-            <v>0</v>
-          </cell>
-          <cell r="AV9">
-            <v>0</v>
-          </cell>
-          <cell r="AW9">
-            <v>0</v>
-          </cell>
-          <cell r="AX9">
-            <v>0</v>
-          </cell>
-          <cell r="AY9">
-            <v>98.71</v>
-          </cell>
-          <cell r="AZ9">
             <v>100</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink10.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="results"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="3">
+          <cell r="AK3">
+            <v>14.61</v>
+          </cell>
+          <cell r="AL3">
+            <v>17.72</v>
+          </cell>
+          <cell r="AM3">
+            <v>0</v>
+          </cell>
+          <cell r="AN3">
+            <v>67.680000000000007</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="AK4">
+            <v>14.61</v>
+          </cell>
+          <cell r="AL4">
+            <v>0</v>
+          </cell>
+          <cell r="AM4">
+            <v>85.4</v>
+          </cell>
+          <cell r="AN4">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="AK5">
+            <v>14.61</v>
+          </cell>
+          <cell r="AL5">
+            <v>0</v>
+          </cell>
+          <cell r="AM5">
+            <v>85.4</v>
+          </cell>
+          <cell r="AN5">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink11.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="results"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="3">
+          <cell r="AK3">
+            <v>11.95</v>
+          </cell>
+          <cell r="AL3">
+            <v>14.5</v>
+          </cell>
+          <cell r="AM3">
+            <v>0</v>
+          </cell>
+          <cell r="AN3">
+            <v>73.55</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="AK4">
+            <v>11.95</v>
+          </cell>
+          <cell r="AL4">
+            <v>0</v>
+          </cell>
+          <cell r="AM4">
+            <v>88.06</v>
+          </cell>
+          <cell r="AN4">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="AK5">
+            <v>11.95</v>
+          </cell>
+          <cell r="AL5">
+            <v>0</v>
+          </cell>
+          <cell r="AM5">
+            <v>88.06</v>
+          </cell>
+          <cell r="AN5">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3480,30 +2945,6 @@
           <cell r="AQ3" t="str">
             <v>minCO2</v>
           </cell>
-          <cell r="AR3">
-            <v>26.550000000000004</v>
-          </cell>
-          <cell r="AS3">
-            <v>32.229999999999997</v>
-          </cell>
-          <cell r="AT3">
-            <v>0</v>
-          </cell>
-          <cell r="AU3">
-            <v>0</v>
-          </cell>
-          <cell r="AV3">
-            <v>41.23</v>
-          </cell>
-          <cell r="AW3">
-            <v>0</v>
-          </cell>
-          <cell r="AX3">
-            <v>0</v>
-          </cell>
-          <cell r="AY3">
-            <v>0</v>
-          </cell>
           <cell r="AZ3">
             <v>100.00999999999999</v>
           </cell>
@@ -3512,30 +2953,6 @@
           <cell r="AQ4" t="str">
             <v>minEQ</v>
           </cell>
-          <cell r="AR4">
-            <v>26.550000000000004</v>
-          </cell>
-          <cell r="AS4">
-            <v>0</v>
-          </cell>
-          <cell r="AT4">
-            <v>0</v>
-          </cell>
-          <cell r="AU4">
-            <v>73.459999999999994</v>
-          </cell>
-          <cell r="AV4">
-            <v>0</v>
-          </cell>
-          <cell r="AW4">
-            <v>0</v>
-          </cell>
-          <cell r="AX4">
-            <v>0</v>
-          </cell>
-          <cell r="AY4">
-            <v>0</v>
-          </cell>
           <cell r="AZ4">
             <v>100.00999999999999</v>
           </cell>
@@ -3544,159 +2961,7 @@
           <cell r="AQ5" t="str">
             <v>minHH</v>
           </cell>
-          <cell r="AR5">
-            <v>26.550000000000004</v>
-          </cell>
-          <cell r="AS5">
-            <v>0</v>
-          </cell>
-          <cell r="AT5">
-            <v>0</v>
-          </cell>
-          <cell r="AU5">
-            <v>73.459999999999994</v>
-          </cell>
-          <cell r="AV5">
-            <v>0</v>
-          </cell>
-          <cell r="AW5">
-            <v>0</v>
-          </cell>
-          <cell r="AX5">
-            <v>0</v>
-          </cell>
-          <cell r="AY5">
-            <v>0</v>
-          </cell>
           <cell r="AZ5">
-            <v>100.00999999999999</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="AQ6" t="str">
-            <v>minEQ&amp;HH</v>
-          </cell>
-          <cell r="AR6">
-            <v>26.550000000000004</v>
-          </cell>
-          <cell r="AS6">
-            <v>0</v>
-          </cell>
-          <cell r="AT6">
-            <v>0</v>
-          </cell>
-          <cell r="AU6">
-            <v>73.459999999999994</v>
-          </cell>
-          <cell r="AV6">
-            <v>0</v>
-          </cell>
-          <cell r="AW6">
-            <v>0</v>
-          </cell>
-          <cell r="AX6">
-            <v>0</v>
-          </cell>
-          <cell r="AY6">
-            <v>0</v>
-          </cell>
-          <cell r="AZ6">
-            <v>100.00999999999999</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="AQ7" t="str">
-            <v>minCO2&amp;EQ</v>
-          </cell>
-          <cell r="AR7">
-            <v>26.550000000000004</v>
-          </cell>
-          <cell r="AS7">
-            <v>0</v>
-          </cell>
-          <cell r="AT7">
-            <v>0</v>
-          </cell>
-          <cell r="AU7">
-            <v>73.459999999999994</v>
-          </cell>
-          <cell r="AV7">
-            <v>0</v>
-          </cell>
-          <cell r="AW7">
-            <v>0</v>
-          </cell>
-          <cell r="AX7">
-            <v>0</v>
-          </cell>
-          <cell r="AY7">
-            <v>0</v>
-          </cell>
-          <cell r="AZ7">
-            <v>100.00999999999999</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="AQ8" t="str">
-            <v>minCO2&amp;HH</v>
-          </cell>
-          <cell r="AR8">
-            <v>26.550000000000004</v>
-          </cell>
-          <cell r="AS8">
-            <v>26.729999999999997</v>
-          </cell>
-          <cell r="AT8">
-            <v>0</v>
-          </cell>
-          <cell r="AU8">
-            <v>46.73</v>
-          </cell>
-          <cell r="AV8">
-            <v>0</v>
-          </cell>
-          <cell r="AW8">
-            <v>0</v>
-          </cell>
-          <cell r="AX8">
-            <v>0</v>
-          </cell>
-          <cell r="AY8">
-            <v>0</v>
-          </cell>
-          <cell r="AZ8">
-            <v>100.00999999999999</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="AQ9" t="str">
-            <v>minCO2&amp;EQ&amp;HH</v>
-          </cell>
-          <cell r="AR9">
-            <v>26.550000000000004</v>
-          </cell>
-          <cell r="AS9">
-            <v>0</v>
-          </cell>
-          <cell r="AT9">
-            <v>0</v>
-          </cell>
-          <cell r="AU9">
-            <v>73.459999999999994</v>
-          </cell>
-          <cell r="AV9">
-            <v>0</v>
-          </cell>
-          <cell r="AW9">
-            <v>0</v>
-          </cell>
-          <cell r="AX9">
-            <v>0</v>
-          </cell>
-          <cell r="AY9">
-            <v>0</v>
-          </cell>
-          <cell r="AZ9">
             <v>100.00999999999999</v>
           </cell>
         </row>
@@ -3747,203 +3012,15 @@
           <cell r="AQ3" t="str">
             <v>minCO2</v>
           </cell>
-          <cell r="AR3">
-            <v>8.86</v>
-          </cell>
-          <cell r="AS3">
-            <v>0</v>
-          </cell>
-          <cell r="AT3">
-            <v>0</v>
-          </cell>
-          <cell r="AU3">
-            <v>0</v>
-          </cell>
-          <cell r="AV3">
-            <v>0</v>
-          </cell>
-          <cell r="AW3">
-            <v>0</v>
-          </cell>
-          <cell r="AX3">
-            <v>0</v>
-          </cell>
-          <cell r="AY3">
-            <v>91.15</v>
-          </cell>
         </row>
         <row r="4">
           <cell r="AQ4" t="str">
             <v>minEQ</v>
           </cell>
-          <cell r="AR4">
-            <v>0</v>
-          </cell>
-          <cell r="AS4">
-            <v>0</v>
-          </cell>
-          <cell r="AT4">
-            <v>0</v>
-          </cell>
-          <cell r="AU4">
-            <v>0</v>
-          </cell>
-          <cell r="AV4">
-            <v>0</v>
-          </cell>
-          <cell r="AW4">
-            <v>0</v>
-          </cell>
-          <cell r="AX4">
-            <v>0</v>
-          </cell>
-          <cell r="AY4">
-            <v>100</v>
-          </cell>
         </row>
         <row r="5">
           <cell r="AQ5" t="str">
             <v>minHH</v>
-          </cell>
-          <cell r="AR5">
-            <v>1.29</v>
-          </cell>
-          <cell r="AS5">
-            <v>0</v>
-          </cell>
-          <cell r="AT5">
-            <v>0</v>
-          </cell>
-          <cell r="AU5">
-            <v>0</v>
-          </cell>
-          <cell r="AV5">
-            <v>0</v>
-          </cell>
-          <cell r="AW5">
-            <v>0</v>
-          </cell>
-          <cell r="AX5">
-            <v>0</v>
-          </cell>
-          <cell r="AY5">
-            <v>98.71</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="AQ6" t="str">
-            <v>minEQ&amp;HH</v>
-          </cell>
-          <cell r="AR6">
-            <v>0</v>
-          </cell>
-          <cell r="AS6">
-            <v>0</v>
-          </cell>
-          <cell r="AT6">
-            <v>0</v>
-          </cell>
-          <cell r="AU6">
-            <v>0</v>
-          </cell>
-          <cell r="AV6">
-            <v>0</v>
-          </cell>
-          <cell r="AW6">
-            <v>0</v>
-          </cell>
-          <cell r="AX6">
-            <v>0</v>
-          </cell>
-          <cell r="AY6">
-            <v>100</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="AQ7" t="str">
-            <v>minCO2&amp;EQ</v>
-          </cell>
-          <cell r="AR7">
-            <v>1.29</v>
-          </cell>
-          <cell r="AS7">
-            <v>0</v>
-          </cell>
-          <cell r="AT7">
-            <v>0</v>
-          </cell>
-          <cell r="AU7">
-            <v>0</v>
-          </cell>
-          <cell r="AV7">
-            <v>0</v>
-          </cell>
-          <cell r="AW7">
-            <v>0</v>
-          </cell>
-          <cell r="AX7">
-            <v>0</v>
-          </cell>
-          <cell r="AY7">
-            <v>98.71</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="AQ8" t="str">
-            <v>minCO2&amp;HH</v>
-          </cell>
-          <cell r="AR8">
-            <v>8.86</v>
-          </cell>
-          <cell r="AS8">
-            <v>0</v>
-          </cell>
-          <cell r="AT8">
-            <v>0</v>
-          </cell>
-          <cell r="AU8">
-            <v>0</v>
-          </cell>
-          <cell r="AV8">
-            <v>0</v>
-          </cell>
-          <cell r="AW8">
-            <v>0</v>
-          </cell>
-          <cell r="AX8">
-            <v>0</v>
-          </cell>
-          <cell r="AY8">
-            <v>91.15</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="AQ9" t="str">
-            <v>minCO2&amp;EQ&amp;HH</v>
-          </cell>
-          <cell r="AR9">
-            <v>1.29</v>
-          </cell>
-          <cell r="AS9">
-            <v>0</v>
-          </cell>
-          <cell r="AT9">
-            <v>0</v>
-          </cell>
-          <cell r="AU9">
-            <v>0</v>
-          </cell>
-          <cell r="AV9">
-            <v>0</v>
-          </cell>
-          <cell r="AW9">
-            <v>0</v>
-          </cell>
-          <cell r="AX9">
-            <v>0</v>
-          </cell>
-          <cell r="AY9">
-            <v>98.71</v>
           </cell>
         </row>
       </sheetData>
@@ -3956,11 +3033,14 @@
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
+      <sheetName val="Contrainte de capacité"/>
       <sheetName val="results"/>
-      <sheetName val="Contrainte de capacité"/>
+      <sheetName val="Feuil1"/>
+      <sheetName val="Feuil2"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0">
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
         <row r="2">
           <cell r="AK2" t="str">
             <v>HC</v>
@@ -3977,7 +3057,7 @@
         </row>
         <row r="3">
           <cell r="AJ3" t="str">
-            <v>minCO2</v>
+            <v>minCC</v>
           </cell>
           <cell r="AK3">
             <v>13.280000000000001</v>
@@ -4026,76 +3106,9 @@
             <v>0</v>
           </cell>
         </row>
-        <row r="6">
-          <cell r="AJ6" t="str">
-            <v>minEQ&amp;HH</v>
-          </cell>
-          <cell r="AK6">
-            <v>13.280000000000001</v>
-          </cell>
-          <cell r="AL6">
-            <v>0</v>
-          </cell>
-          <cell r="AM6">
-            <v>86.73</v>
-          </cell>
-          <cell r="AN6">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="AJ7" t="str">
-            <v>minCO2&amp;EQ</v>
-          </cell>
-          <cell r="AK7">
-            <v>13.280000000000001</v>
-          </cell>
-          <cell r="AL7">
-            <v>0</v>
-          </cell>
-          <cell r="AM7">
-            <v>86.73</v>
-          </cell>
-          <cell r="AN7">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="AJ8" t="str">
-            <v>minCO2&amp;HH</v>
-          </cell>
-          <cell r="AK8">
-            <v>13.280000000000001</v>
-          </cell>
-          <cell r="AL8">
-            <v>6.6999999999999993</v>
-          </cell>
-          <cell r="AM8">
-            <v>80.03</v>
-          </cell>
-          <cell r="AN8">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="AJ9" t="str">
-            <v>minCO2&amp;EQ&amp;HH</v>
-          </cell>
-          <cell r="AK9">
-            <v>13.280000000000001</v>
-          </cell>
-          <cell r="AL9">
-            <v>0</v>
-          </cell>
-          <cell r="AM9">
-            <v>86.73</v>
-          </cell>
-          <cell r="AN9">
-            <v>0</v>
-          </cell>
-        </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4130,18 +3143,6 @@
           <cell r="AJ3" t="str">
             <v>minCO2</v>
           </cell>
-          <cell r="AK3">
-            <v>26.550000000000004</v>
-          </cell>
-          <cell r="AL3">
-            <v>32.229999999999997</v>
-          </cell>
-          <cell r="AM3">
-            <v>0</v>
-          </cell>
-          <cell r="AN3">
-            <v>41.23</v>
-          </cell>
           <cell r="AO3">
             <v>100.00999999999999</v>
           </cell>
@@ -4150,18 +3151,6 @@
           <cell r="AJ4" t="str">
             <v>minEQ</v>
           </cell>
-          <cell r="AK4">
-            <v>26.550000000000004</v>
-          </cell>
-          <cell r="AL4">
-            <v>0</v>
-          </cell>
-          <cell r="AM4">
-            <v>73.459999999999994</v>
-          </cell>
-          <cell r="AN4">
-            <v>0</v>
-          </cell>
           <cell r="AO4">
             <v>100.00999999999999</v>
           </cell>
@@ -4170,99 +3159,7 @@
           <cell r="AJ5" t="str">
             <v>minHH</v>
           </cell>
-          <cell r="AK5">
-            <v>26.550000000000004</v>
-          </cell>
-          <cell r="AL5">
-            <v>0</v>
-          </cell>
-          <cell r="AM5">
-            <v>73.459999999999994</v>
-          </cell>
-          <cell r="AN5">
-            <v>0</v>
-          </cell>
           <cell r="AO5">
-            <v>100.00999999999999</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="AJ6" t="str">
-            <v>minEQ&amp;HH</v>
-          </cell>
-          <cell r="AK6">
-            <v>26.550000000000004</v>
-          </cell>
-          <cell r="AL6">
-            <v>0</v>
-          </cell>
-          <cell r="AM6">
-            <v>73.459999999999994</v>
-          </cell>
-          <cell r="AN6">
-            <v>0</v>
-          </cell>
-          <cell r="AO6">
-            <v>100.00999999999999</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="AJ7" t="str">
-            <v>minCO2&amp;EQ</v>
-          </cell>
-          <cell r="AK7">
-            <v>26.550000000000004</v>
-          </cell>
-          <cell r="AL7">
-            <v>0</v>
-          </cell>
-          <cell r="AM7">
-            <v>73.459999999999994</v>
-          </cell>
-          <cell r="AN7">
-            <v>0</v>
-          </cell>
-          <cell r="AO7">
-            <v>100.00999999999999</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="AJ8" t="str">
-            <v>minCO2&amp;HH</v>
-          </cell>
-          <cell r="AK8">
-            <v>26.550000000000004</v>
-          </cell>
-          <cell r="AL8">
-            <v>26.729999999999997</v>
-          </cell>
-          <cell r="AM8">
-            <v>46.73</v>
-          </cell>
-          <cell r="AN8">
-            <v>0</v>
-          </cell>
-          <cell r="AO8">
-            <v>100.00999999999999</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="AJ9" t="str">
-            <v>minCO2&amp;EQ&amp;HH</v>
-          </cell>
-          <cell r="AK9">
-            <v>26.550000000000004</v>
-          </cell>
-          <cell r="AL9">
-            <v>0</v>
-          </cell>
-          <cell r="AM9">
-            <v>73.459999999999994</v>
-          </cell>
-          <cell r="AN9">
-            <v>0</v>
-          </cell>
-          <cell r="AO9">
             <v>100.00999999999999</v>
           </cell>
         </row>
@@ -4301,18 +3198,6 @@
           <cell r="AJ3" t="str">
             <v>minCO2</v>
           </cell>
-          <cell r="AK3">
-            <v>8.86</v>
-          </cell>
-          <cell r="AL3">
-            <v>6.95</v>
-          </cell>
-          <cell r="AM3">
-            <v>32.25</v>
-          </cell>
-          <cell r="AN3">
-            <v>51.95</v>
-          </cell>
           <cell r="AO3">
             <v>100.01</v>
           </cell>
@@ -4321,18 +3206,6 @@
           <cell r="AJ4" t="str">
             <v>minEQ</v>
           </cell>
-          <cell r="AK4">
-            <v>8.86</v>
-          </cell>
-          <cell r="AL4">
-            <v>3.41</v>
-          </cell>
-          <cell r="AM4">
-            <v>62.34</v>
-          </cell>
-          <cell r="AN4">
-            <v>25.4</v>
-          </cell>
           <cell r="AO4">
             <v>100.00999999999999</v>
           </cell>
@@ -4341,100 +3214,284 @@
           <cell r="AJ5" t="str">
             <v>minHH</v>
           </cell>
-          <cell r="AK5">
-            <v>8.86</v>
-          </cell>
-          <cell r="AL5">
-            <v>3.41</v>
-          </cell>
-          <cell r="AM5">
-            <v>62.34</v>
-          </cell>
-          <cell r="AN5">
-            <v>25.4</v>
-          </cell>
           <cell r="AO5">
             <v>100.00999999999999</v>
           </cell>
         </row>
-        <row r="6">
-          <cell r="AJ6" t="str">
-            <v>minEQ&amp;HH</v>
-          </cell>
-          <cell r="AK6">
-            <v>8.86</v>
-          </cell>
-          <cell r="AL6">
-            <v>3.41</v>
-          </cell>
-          <cell r="AM6">
-            <v>62.34</v>
-          </cell>
-          <cell r="AN6">
-            <v>25.4</v>
-          </cell>
-          <cell r="AO6">
-            <v>100.00999999999999</v>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink7.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="results"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="3">
+          <cell r="AR3">
+            <v>6.5</v>
+          </cell>
+          <cell r="AS3">
+            <v>0</v>
+          </cell>
+          <cell r="AT3">
+            <v>0</v>
+          </cell>
+          <cell r="AU3">
+            <v>0</v>
+          </cell>
+          <cell r="AV3">
+            <v>0</v>
+          </cell>
+          <cell r="AW3">
+            <v>93.51</v>
+          </cell>
+          <cell r="AX3">
+            <v>0</v>
+          </cell>
+          <cell r="AY3">
+            <v>0</v>
           </cell>
         </row>
-        <row r="7">
-          <cell r="AJ7" t="str">
-            <v>minCO2&amp;EQ</v>
-          </cell>
-          <cell r="AK7">
-            <v>8.86</v>
-          </cell>
-          <cell r="AL7">
-            <v>3.41</v>
-          </cell>
-          <cell r="AM7">
-            <v>62.34</v>
-          </cell>
-          <cell r="AN7">
-            <v>25.4</v>
-          </cell>
-          <cell r="AO7">
-            <v>100.00999999999999</v>
+        <row r="4">
+          <cell r="AR4">
+            <v>0</v>
+          </cell>
+          <cell r="AS4">
+            <v>0</v>
+          </cell>
+          <cell r="AT4">
+            <v>0</v>
+          </cell>
+          <cell r="AU4">
+            <v>0</v>
+          </cell>
+          <cell r="AV4">
+            <v>0</v>
+          </cell>
+          <cell r="AW4">
+            <v>0</v>
+          </cell>
+          <cell r="AX4">
+            <v>0</v>
+          </cell>
+          <cell r="AY4">
+            <v>100</v>
           </cell>
         </row>
-        <row r="8">
-          <cell r="AJ8" t="str">
-            <v>minCO2&amp;HH</v>
-          </cell>
-          <cell r="AK8">
-            <v>8.86</v>
-          </cell>
-          <cell r="AL8">
-            <v>3.41</v>
-          </cell>
-          <cell r="AM8">
-            <v>62.34</v>
-          </cell>
-          <cell r="AN8">
-            <v>25.4</v>
-          </cell>
-          <cell r="AO8">
-            <v>100.00999999999999</v>
+        <row r="5">
+          <cell r="AR5">
+            <v>1.29</v>
+          </cell>
+          <cell r="AS5">
+            <v>0</v>
+          </cell>
+          <cell r="AT5">
+            <v>0</v>
+          </cell>
+          <cell r="AU5">
+            <v>0</v>
+          </cell>
+          <cell r="AV5">
+            <v>0</v>
+          </cell>
+          <cell r="AW5">
+            <v>0</v>
+          </cell>
+          <cell r="AX5">
+            <v>0</v>
+          </cell>
+          <cell r="AY5">
+            <v>98.71</v>
           </cell>
         </row>
-        <row r="9">
-          <cell r="AJ9" t="str">
-            <v>minCO2&amp;EQ&amp;HH</v>
-          </cell>
-          <cell r="AK9">
-            <v>8.86</v>
-          </cell>
-          <cell r="AL9">
-            <v>3.41</v>
-          </cell>
-          <cell r="AM9">
-            <v>62.34</v>
-          </cell>
-          <cell r="AN9">
-            <v>25.4</v>
-          </cell>
-          <cell r="AO9">
-            <v>100.00999999999999</v>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink8.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="results"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="3">
+          <cell r="AR3">
+            <v>6.5</v>
+          </cell>
+          <cell r="AS3">
+            <v>0</v>
+          </cell>
+          <cell r="AT3">
+            <v>0</v>
+          </cell>
+          <cell r="AU3">
+            <v>0</v>
+          </cell>
+          <cell r="AV3">
+            <v>0</v>
+          </cell>
+          <cell r="AW3">
+            <v>93.51</v>
+          </cell>
+          <cell r="AX3">
+            <v>0</v>
+          </cell>
+          <cell r="AY3">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="AR4">
+            <v>0</v>
+          </cell>
+          <cell r="AS4">
+            <v>0</v>
+          </cell>
+          <cell r="AT4">
+            <v>0</v>
+          </cell>
+          <cell r="AU4">
+            <v>0</v>
+          </cell>
+          <cell r="AV4">
+            <v>0</v>
+          </cell>
+          <cell r="AW4">
+            <v>0</v>
+          </cell>
+          <cell r="AX4">
+            <v>0</v>
+          </cell>
+          <cell r="AY4">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="AR5">
+            <v>1.29</v>
+          </cell>
+          <cell r="AS5">
+            <v>0</v>
+          </cell>
+          <cell r="AT5">
+            <v>0</v>
+          </cell>
+          <cell r="AU5">
+            <v>0</v>
+          </cell>
+          <cell r="AV5">
+            <v>0</v>
+          </cell>
+          <cell r="AW5">
+            <v>0</v>
+          </cell>
+          <cell r="AX5">
+            <v>0</v>
+          </cell>
+          <cell r="AY5">
+            <v>98.71</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink9.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="results"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="3">
+          <cell r="AR3">
+            <v>6.5</v>
+          </cell>
+          <cell r="AS3">
+            <v>0</v>
+          </cell>
+          <cell r="AT3">
+            <v>0</v>
+          </cell>
+          <cell r="AU3">
+            <v>0</v>
+          </cell>
+          <cell r="AV3">
+            <v>0</v>
+          </cell>
+          <cell r="AW3">
+            <v>93.51</v>
+          </cell>
+          <cell r="AX3">
+            <v>0</v>
+          </cell>
+          <cell r="AY3">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="AR4">
+            <v>0</v>
+          </cell>
+          <cell r="AS4">
+            <v>0</v>
+          </cell>
+          <cell r="AT4">
+            <v>0</v>
+          </cell>
+          <cell r="AU4">
+            <v>0</v>
+          </cell>
+          <cell r="AV4">
+            <v>0</v>
+          </cell>
+          <cell r="AW4">
+            <v>0</v>
+          </cell>
+          <cell r="AX4">
+            <v>0</v>
+          </cell>
+          <cell r="AY4">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="AR5">
+            <v>1.29</v>
+          </cell>
+          <cell r="AS5">
+            <v>0</v>
+          </cell>
+          <cell r="AT5">
+            <v>0</v>
+          </cell>
+          <cell r="AU5">
+            <v>0</v>
+          </cell>
+          <cell r="AV5">
+            <v>0</v>
+          </cell>
+          <cell r="AW5">
+            <v>0</v>
+          </cell>
+          <cell r="AX5">
+            <v>0</v>
+          </cell>
+          <cell r="AY5">
+            <v>98.71</v>
           </cell>
         </row>
       </sheetData>
@@ -4706,24 +3763,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:AG30"/>
+  <dimension ref="A2:AI14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="0" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="11.7265625" customWidth="1"/>
+    <col min="9" max="9" width="12.453125" customWidth="1"/>
+    <col min="10" max="12" width="19.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
-      <c r="N2" t="s">
+      <c r="P2" t="s">
         <v>2</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="AA2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A3" t="str">
         <f>[1]results!AQ2</f>
         <v>name</v>
@@ -4760,253 +3820,253 @@
         <f>[1]results!AY2</f>
         <v>AD-heat-comp</v>
       </c>
-      <c r="K3">
+      <c r="M3">
         <f>[1]results!AZ2</f>
         <v>0</v>
       </c>
-      <c r="N3" t="str">
+      <c r="P3" t="str">
         <f>[2]results!AQ2</f>
         <v>name</v>
       </c>
-      <c r="O3" t="str">
+      <c r="Q3" t="str">
         <f>[2]results!AR2</f>
         <v>HC</v>
       </c>
-      <c r="P3" t="str">
+      <c r="R3" t="str">
         <f>[2]results!AS2</f>
         <v>IC</v>
       </c>
-      <c r="Q3" t="str">
+      <c r="S3" t="str">
         <f>[2]results!AT2</f>
         <v>AD-cog-dig</v>
       </c>
-      <c r="R3" t="str">
+      <c r="T3" t="str">
         <f>[2]results!AU2</f>
         <v>AD-cog-comp</v>
       </c>
-      <c r="S3" t="str">
+      <c r="U3" t="str">
         <f>[2]results!AV2</f>
         <v>AD-biomet-dig</v>
       </c>
-      <c r="T3" t="str">
+      <c r="V3" t="str">
         <f>[2]results!AW2</f>
         <v>AD-biomet-comp</v>
       </c>
-      <c r="U3" t="str">
+      <c r="W3" t="str">
         <f>[2]results!AX2</f>
         <v>AD-heat-dig</v>
       </c>
-      <c r="V3" t="str">
+      <c r="X3" t="str">
         <f>[2]results!AY2</f>
         <v>AD-heat-comp</v>
       </c>
-      <c r="W3">
+      <c r="Y3">
         <f>[2]results!AZ2</f>
         <v>0</v>
       </c>
-      <c r="Y3" t="str">
+      <c r="AA3" t="str">
         <f>[3]results!AQ2</f>
         <v>name</v>
       </c>
-      <c r="Z3" t="str">
+      <c r="AB3" t="str">
         <f>[3]results!AR2</f>
         <v>HC</v>
       </c>
-      <c r="AA3" t="str">
+      <c r="AC3" t="str">
         <f>[3]results!AS2</f>
         <v>IC</v>
       </c>
-      <c r="AB3" t="str">
+      <c r="AD3" t="str">
         <f>[3]results!AT2</f>
         <v>AD-cog-dig</v>
       </c>
-      <c r="AC3" t="str">
+      <c r="AE3" t="str">
         <f>[3]results!AU2</f>
         <v>AD-cog-comp</v>
       </c>
-      <c r="AD3" t="str">
+      <c r="AF3" t="str">
         <f>[3]results!AV2</f>
         <v>AD-biomet-dig</v>
       </c>
-      <c r="AE3" t="str">
+      <c r="AG3" t="str">
         <f>[3]results!AW2</f>
         <v>AD-biomet-comp</v>
       </c>
-      <c r="AF3" t="str">
+      <c r="AH3" t="str">
         <f>[3]results!AX2</f>
         <v>AD-heat-dig</v>
       </c>
-      <c r="AG3" t="str">
+      <c r="AI3" t="str">
         <f>[3]results!AY2</f>
         <v>AD-heat-comp</v>
       </c>
     </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.35">
       <c r="B4">
         <v>-0.5</v>
       </c>
       <c r="C4">
-        <f t="shared" ref="C4:K4" si="0">O5</f>
-        <v>26.550000000000004</v>
+        <f>Q5</f>
+        <v>6.5</v>
       </c>
       <c r="D4">
-        <f t="shared" si="0"/>
-        <v>32.229999999999997</v>
+        <f>R5</f>
+        <v>0</v>
       </c>
       <c r="E4">
-        <f t="shared" si="0"/>
+        <f>S5</f>
         <v>0</v>
       </c>
       <c r="F4">
-        <f t="shared" si="0"/>
+        <f>T5</f>
         <v>0</v>
       </c>
       <c r="G4">
-        <f t="shared" si="0"/>
-        <v>41.23</v>
+        <f>U5</f>
+        <v>0</v>
       </c>
       <c r="H4">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>V5</f>
+        <v>93.51</v>
       </c>
       <c r="I4">
-        <f t="shared" si="0"/>
+        <f>W5</f>
         <v>0</v>
       </c>
       <c r="J4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <f t="shared" si="0"/>
+        <f>X5</f>
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <f t="shared" ref="M4" si="0">Y5</f>
         <v>100.00999999999999</v>
       </c>
     </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A5" t="str">
         <f>[1]results!AQ3</f>
-        <v>minCO2</v>
+        <v>minCC</v>
       </c>
       <c r="C5">
-        <f>[1]results!AR3</f>
+        <f>[7]results!AR3</f>
         <v>6.5</v>
       </c>
       <c r="D5">
-        <f>[1]results!AS3</f>
+        <f>[7]results!AS3</f>
         <v>0</v>
       </c>
       <c r="E5">
-        <f>[1]results!AT3</f>
+        <f>[7]results!AT3</f>
         <v>0</v>
       </c>
       <c r="F5">
-        <f>[1]results!AU3</f>
+        <f>[7]results!AU3</f>
         <v>0</v>
       </c>
       <c r="G5">
-        <f>[1]results!AV3</f>
+        <f>[7]results!AV3</f>
         <v>0</v>
       </c>
       <c r="H5">
-        <f>[1]results!AW3</f>
-        <v>0</v>
+        <f>[7]results!AW3</f>
+        <v>93.51</v>
       </c>
       <c r="I5">
-        <f>[1]results!AX3</f>
+        <f>[7]results!AX3</f>
         <v>0</v>
       </c>
       <c r="J5">
-        <f>[1]results!AY3</f>
-        <v>93.51</v>
-      </c>
-      <c r="K5">
+        <f>[7]results!AY3</f>
+        <v>0</v>
+      </c>
+      <c r="M5">
         <f>[1]results!AZ3</f>
         <v>100.01</v>
       </c>
-      <c r="N5" t="str">
+      <c r="P5" t="str">
         <f>[2]results!AQ3</f>
         <v>minCO2</v>
       </c>
-      <c r="O5">
-        <f>[2]results!AR3</f>
-        <v>26.550000000000004</v>
-      </c>
-      <c r="P5">
-        <f>[2]results!AS3</f>
-        <v>32.229999999999997</v>
-      </c>
       <c r="Q5">
-        <f>[2]results!AT3</f>
-        <v>0</v>
+        <f>[9]results!AR3</f>
+        <v>6.5</v>
       </c>
       <c r="R5">
-        <f>[2]results!AU3</f>
+        <f>[9]results!AS3</f>
         <v>0</v>
       </c>
       <c r="S5">
-        <f>[2]results!AV3</f>
-        <v>41.23</v>
+        <f>[9]results!AT3</f>
+        <v>0</v>
       </c>
       <c r="T5">
-        <f>[2]results!AW3</f>
+        <f>[9]results!AU3</f>
         <v>0</v>
       </c>
       <c r="U5">
-        <f>[2]results!AX3</f>
+        <f>[9]results!AV3</f>
         <v>0</v>
       </c>
       <c r="V5">
-        <f>[2]results!AY3</f>
-        <v>0</v>
+        <f>[9]results!AW3</f>
+        <v>93.51</v>
       </c>
       <c r="W5">
+        <f>[9]results!AX3</f>
+        <v>0</v>
+      </c>
+      <c r="X5">
+        <f>[9]results!AY3</f>
+        <v>0</v>
+      </c>
+      <c r="Y5">
         <f>[2]results!AZ3</f>
         <v>100.00999999999999</v>
       </c>
-      <c r="Y5" t="str">
+      <c r="AA5" t="str">
         <f>[3]results!AQ3</f>
         <v>minCO2</v>
       </c>
-      <c r="Z5">
-        <f>[3]results!AR3</f>
-        <v>8.86</v>
-      </c>
-      <c r="AA5">
-        <f>[3]results!AS3</f>
-        <v>0</v>
-      </c>
       <c r="AB5">
-        <f>[3]results!AT3</f>
-        <v>0</v>
+        <f>[8]results!AR3</f>
+        <v>6.5</v>
       </c>
       <c r="AC5">
-        <f>[3]results!AU3</f>
+        <f>[8]results!AS3</f>
         <v>0</v>
       </c>
       <c r="AD5">
-        <f>[3]results!AV3</f>
+        <f>[8]results!AT3</f>
         <v>0</v>
       </c>
       <c r="AE5">
-        <f>[3]results!AW3</f>
+        <f>[8]results!AU3</f>
         <v>0</v>
       </c>
       <c r="AF5">
-        <f>[3]results!AX3</f>
+        <f>[8]results!AV3</f>
         <v>0</v>
       </c>
       <c r="AG5">
-        <f>[3]results!AY3</f>
-        <v>91.15</v>
+        <f>[8]results!AW3</f>
+        <v>93.51</v>
+      </c>
+      <c r="AH5">
+        <f>[8]results!AX3</f>
+        <v>0</v>
+      </c>
+      <c r="AI5">
+        <f>[8]results!AY3</f>
+        <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.35">
       <c r="B6">
         <v>0.5</v>
       </c>
       <c r="C6">
-        <f t="shared" ref="C6:J6" si="1">Z5</f>
-        <v>8.86</v>
+        <f t="shared" ref="C6:J6" si="1">AB5</f>
+        <v>6.5</v>
       </c>
       <c r="D6">
         <f t="shared" si="1"/>
@@ -5026,7 +4086,7 @@
       </c>
       <c r="H6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>93.51</v>
       </c>
       <c r="I6">
         <f t="shared" si="1"/>
@@ -5034,174 +4094,174 @@
       </c>
       <c r="J6">
         <f t="shared" si="1"/>
-        <v>91.15</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.35">
       <c r="B8">
         <v>-0.5</v>
       </c>
       <c r="C8">
-        <f t="shared" ref="C8:K8" si="2">O9</f>
-        <v>26.550000000000004</v>
+        <f>Q9</f>
+        <v>0</v>
       </c>
       <c r="D8">
-        <f t="shared" si="2"/>
+        <f>R9</f>
         <v>0</v>
       </c>
       <c r="E8">
-        <f t="shared" si="2"/>
+        <f>S9</f>
         <v>0</v>
       </c>
       <c r="F8">
-        <f t="shared" si="2"/>
-        <v>73.459999999999994</v>
+        <f>T9</f>
+        <v>0</v>
       </c>
       <c r="G8">
-        <f t="shared" si="2"/>
+        <f>U9</f>
         <v>0</v>
       </c>
       <c r="H8">
-        <f t="shared" si="2"/>
+        <f>V9</f>
         <v>0</v>
       </c>
       <c r="I8">
-        <f t="shared" si="2"/>
+        <f>W9</f>
         <v>0</v>
       </c>
       <c r="J8">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <f t="shared" si="2"/>
+        <f>X9</f>
+        <v>100</v>
+      </c>
+      <c r="M8">
+        <f t="shared" ref="M8" si="2">Y9</f>
         <v>100.00999999999999</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A9" t="str">
         <f>[1]results!AQ4</f>
         <v>minEQ</v>
       </c>
       <c r="C9">
-        <f>[1]results!AR4</f>
+        <f>[7]results!AR4</f>
         <v>0</v>
       </c>
       <c r="D9">
-        <f>[1]results!AS4</f>
+        <f>[7]results!AS4</f>
         <v>0</v>
       </c>
       <c r="E9">
-        <f>[1]results!AT4</f>
+        <f>[7]results!AT4</f>
         <v>0</v>
       </c>
       <c r="F9">
-        <f>[1]results!AU4</f>
+        <f>[7]results!AU4</f>
         <v>0</v>
       </c>
       <c r="G9">
-        <f>[1]results!AV4</f>
+        <f>[7]results!AV4</f>
         <v>0</v>
       </c>
       <c r="H9">
-        <f>[1]results!AW4</f>
+        <f>[7]results!AW4</f>
         <v>0</v>
       </c>
       <c r="I9">
-        <f>[1]results!AX4</f>
+        <f>[7]results!AX4</f>
         <v>0</v>
       </c>
       <c r="J9">
-        <f>[1]results!AY4</f>
+        <f>[7]results!AY4</f>
         <v>100</v>
       </c>
-      <c r="K9">
+      <c r="M9">
         <f>[1]results!AZ4</f>
         <v>100</v>
       </c>
-      <c r="N9" t="str">
+      <c r="P9" t="str">
         <f>[2]results!AQ4</f>
         <v>minEQ</v>
       </c>
-      <c r="O9">
-        <f>[2]results!AR4</f>
-        <v>26.550000000000004</v>
-      </c>
-      <c r="P9">
-        <f>[2]results!AS4</f>
-        <v>0</v>
-      </c>
       <c r="Q9">
-        <f>[2]results!AT4</f>
+        <f>[9]results!AR4</f>
         <v>0</v>
       </c>
       <c r="R9">
-        <f>[2]results!AU4</f>
-        <v>73.459999999999994</v>
+        <f>[9]results!AS4</f>
+        <v>0</v>
       </c>
       <c r="S9">
-        <f>[2]results!AV4</f>
+        <f>[9]results!AT4</f>
         <v>0</v>
       </c>
       <c r="T9">
-        <f>[2]results!AW4</f>
+        <f>[9]results!AU4</f>
         <v>0</v>
       </c>
       <c r="U9">
-        <f>[2]results!AX4</f>
+        <f>[9]results!AV4</f>
         <v>0</v>
       </c>
       <c r="V9">
-        <f>[2]results!AY4</f>
+        <f>[9]results!AW4</f>
         <v>0</v>
       </c>
       <c r="W9">
+        <f>[9]results!AX4</f>
+        <v>0</v>
+      </c>
+      <c r="X9">
+        <f>[9]results!AY4</f>
+        <v>100</v>
+      </c>
+      <c r="Y9">
         <f>[2]results!AZ4</f>
         <v>100.00999999999999</v>
       </c>
-      <c r="Y9" t="str">
+      <c r="AA9" t="str">
         <f>[3]results!AQ4</f>
         <v>minEQ</v>
       </c>
-      <c r="Z9">
-        <f>[3]results!AR4</f>
-        <v>0</v>
-      </c>
-      <c r="AA9">
-        <f>[3]results!AS4</f>
-        <v>0</v>
-      </c>
       <c r="AB9">
-        <f>[3]results!AT4</f>
+        <f>[8]results!AR4</f>
         <v>0</v>
       </c>
       <c r="AC9">
-        <f>[3]results!AU4</f>
+        <f>[8]results!AS4</f>
         <v>0</v>
       </c>
       <c r="AD9">
-        <f>[3]results!AV4</f>
+        <f>[8]results!AT4</f>
         <v>0</v>
       </c>
       <c r="AE9">
-        <f>[3]results!AW4</f>
+        <f>[8]results!AU4</f>
         <v>0</v>
       </c>
       <c r="AF9">
-        <f>[3]results!AX4</f>
+        <f>[8]results!AV4</f>
         <v>0</v>
       </c>
       <c r="AG9">
-        <f>[3]results!AY4</f>
+        <f>[8]results!AW4</f>
+        <v>0</v>
+      </c>
+      <c r="AH9">
+        <f>[8]results!AX4</f>
+        <v>0</v>
+      </c>
+      <c r="AI9">
+        <f>[8]results!AY4</f>
         <v>100</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.35">
       <c r="B10">
         <v>0.5</v>
       </c>
       <c r="C10">
-        <f t="shared" ref="C10:J10" si="3">Z9</f>
+        <f t="shared" ref="C10:J10" si="3">AB9</f>
         <v>0</v>
       </c>
       <c r="D10">
@@ -5233,171 +4293,171 @@
         <v>100</v>
       </c>
     </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:35" x14ac:dyDescent="0.35">
       <c r="B12">
         <v>-0.5</v>
       </c>
       <c r="C12">
-        <f t="shared" ref="C12:K12" si="4">O13</f>
-        <v>26.550000000000004</v>
+        <f>Q13</f>
+        <v>1.29</v>
       </c>
       <c r="D12">
-        <f t="shared" si="4"/>
+        <f>R13</f>
         <v>0</v>
       </c>
       <c r="E12">
-        <f t="shared" si="4"/>
+        <f>S13</f>
         <v>0</v>
       </c>
       <c r="F12">
-        <f t="shared" si="4"/>
-        <v>73.459999999999994</v>
+        <f>T13</f>
+        <v>0</v>
       </c>
       <c r="G12">
-        <f t="shared" si="4"/>
+        <f>U13</f>
         <v>0</v>
       </c>
       <c r="H12">
-        <f t="shared" si="4"/>
+        <f>V13</f>
         <v>0</v>
       </c>
       <c r="I12">
-        <f t="shared" si="4"/>
+        <f>W13</f>
         <v>0</v>
       </c>
       <c r="J12">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="K12">
-        <f t="shared" si="4"/>
+        <f>X13</f>
+        <v>98.71</v>
+      </c>
+      <c r="M12">
+        <f t="shared" ref="M12" si="4">Y13</f>
         <v>100.00999999999999</v>
       </c>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A13" t="str">
         <f>[1]results!AQ5</f>
         <v>minHH</v>
       </c>
       <c r="C13">
-        <f>[1]results!AR5</f>
+        <f>[7]results!AR5</f>
         <v>1.29</v>
       </c>
       <c r="D13">
-        <f>[1]results!AS5</f>
+        <f>[7]results!AS5</f>
         <v>0</v>
       </c>
       <c r="E13">
-        <f>[1]results!AT5</f>
+        <f>[7]results!AT5</f>
         <v>0</v>
       </c>
       <c r="F13">
-        <f>[1]results!AU5</f>
+        <f>[7]results!AU5</f>
         <v>0</v>
       </c>
       <c r="G13">
-        <f>[1]results!AV5</f>
+        <f>[7]results!AV5</f>
         <v>0</v>
       </c>
       <c r="H13">
-        <f>[1]results!AW5</f>
+        <f>[7]results!AW5</f>
         <v>0</v>
       </c>
       <c r="I13">
-        <f>[1]results!AX5</f>
+        <f>[7]results!AX5</f>
         <v>0</v>
       </c>
       <c r="J13">
-        <f>[1]results!AY5</f>
+        <f>[7]results!AY5</f>
         <v>98.71</v>
       </c>
-      <c r="K13">
+      <c r="M13">
         <f>[1]results!AZ5</f>
         <v>100</v>
       </c>
-      <c r="N13" t="str">
+      <c r="P13" t="str">
         <f>[2]results!AQ5</f>
         <v>minHH</v>
       </c>
-      <c r="O13">
-        <f>[2]results!AR5</f>
-        <v>26.550000000000004</v>
-      </c>
-      <c r="P13">
-        <f>[2]results!AS5</f>
-        <v>0</v>
-      </c>
       <c r="Q13">
-        <f>[2]results!AT5</f>
-        <v>0</v>
+        <f>[9]results!AR5</f>
+        <v>1.29</v>
       </c>
       <c r="R13">
-        <f>[2]results!AU5</f>
-        <v>73.459999999999994</v>
+        <f>[9]results!AS5</f>
+        <v>0</v>
       </c>
       <c r="S13">
-        <f>[2]results!AV5</f>
+        <f>[9]results!AT5</f>
         <v>0</v>
       </c>
       <c r="T13">
-        <f>[2]results!AW5</f>
+        <f>[9]results!AU5</f>
         <v>0</v>
       </c>
       <c r="U13">
-        <f>[2]results!AX5</f>
+        <f>[9]results!AV5</f>
         <v>0</v>
       </c>
       <c r="V13">
-        <f>[2]results!AY5</f>
+        <f>[9]results!AW5</f>
         <v>0</v>
       </c>
       <c r="W13">
+        <f>[9]results!AX5</f>
+        <v>0</v>
+      </c>
+      <c r="X13">
+        <f>[9]results!AY5</f>
+        <v>98.71</v>
+      </c>
+      <c r="Y13">
         <f>[2]results!AZ5</f>
         <v>100.00999999999999</v>
       </c>
-      <c r="Y13" t="str">
+      <c r="AA13" t="str">
         <f>[3]results!AQ5</f>
         <v>minHH</v>
       </c>
-      <c r="Z13">
-        <f>[3]results!AR5</f>
+      <c r="AB13">
+        <f>[8]results!AR5</f>
         <v>1.29</v>
       </c>
-      <c r="AA13">
-        <f>[3]results!AS5</f>
-        <v>0</v>
-      </c>
-      <c r="AB13">
-        <f>[3]results!AT5</f>
-        <v>0</v>
-      </c>
       <c r="AC13">
-        <f>[3]results!AU5</f>
+        <f>[8]results!AS5</f>
         <v>0</v>
       </c>
       <c r="AD13">
-        <f>[3]results!AV5</f>
+        <f>[8]results!AT5</f>
         <v>0</v>
       </c>
       <c r="AE13">
-        <f>[3]results!AW5</f>
+        <f>[8]results!AU5</f>
         <v>0</v>
       </c>
       <c r="AF13">
-        <f>[3]results!AX5</f>
+        <f>[8]results!AV5</f>
         <v>0</v>
       </c>
       <c r="AG13">
-        <f>[3]results!AY5</f>
+        <f>[8]results!AW5</f>
+        <v>0</v>
+      </c>
+      <c r="AH13">
+        <f>[8]results!AX5</f>
+        <v>0</v>
+      </c>
+      <c r="AI13">
+        <f>[8]results!AY5</f>
         <v>98.71</v>
       </c>
     </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:35" x14ac:dyDescent="0.35">
       <c r="B14">
         <v>0.5</v>
       </c>
       <c r="C14">
-        <f t="shared" ref="C14:J14" si="5">Z13</f>
+        <f t="shared" ref="C14:J14" si="5">AB13</f>
         <v>1.29</v>
       </c>
       <c r="D14">
@@ -5426,790 +4486,6 @@
       </c>
       <c r="J14">
         <f t="shared" si="5"/>
-        <v>98.71</v>
-      </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.35">
-      <c r="B16">
-        <v>-0.5</v>
-      </c>
-      <c r="C16">
-        <f t="shared" ref="C16:K16" si="6">O17</f>
-        <v>26.550000000000004</v>
-      </c>
-      <c r="D16">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="E16">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F16">
-        <f t="shared" si="6"/>
-        <v>73.459999999999994</v>
-      </c>
-      <c r="G16">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="H16">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="I16">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="J16">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="K16">
-        <f t="shared" si="6"/>
-        <v>100.00999999999999</v>
-      </c>
-    </row>
-    <row r="17" spans="1:33" x14ac:dyDescent="0.35">
-      <c r="A17" t="str">
-        <f>[1]results!AQ6</f>
-        <v>minEQ&amp;HH</v>
-      </c>
-      <c r="C17">
-        <f>[1]results!AR6</f>
-        <v>0</v>
-      </c>
-      <c r="D17">
-        <f>[1]results!AS6</f>
-        <v>0</v>
-      </c>
-      <c r="E17">
-        <f>[1]results!AT6</f>
-        <v>0</v>
-      </c>
-      <c r="F17">
-        <f>[1]results!AU6</f>
-        <v>0</v>
-      </c>
-      <c r="G17">
-        <f>[1]results!AV6</f>
-        <v>0</v>
-      </c>
-      <c r="H17">
-        <f>[1]results!AW6</f>
-        <v>0</v>
-      </c>
-      <c r="I17">
-        <f>[1]results!AX6</f>
-        <v>0</v>
-      </c>
-      <c r="J17">
-        <f>[1]results!AY6</f>
-        <v>100</v>
-      </c>
-      <c r="K17">
-        <f>[1]results!AZ6</f>
-        <v>100</v>
-      </c>
-      <c r="N17" t="str">
-        <f>[2]results!AQ6</f>
-        <v>minEQ&amp;HH</v>
-      </c>
-      <c r="O17">
-        <f>[2]results!AR6</f>
-        <v>26.550000000000004</v>
-      </c>
-      <c r="P17">
-        <f>[2]results!AS6</f>
-        <v>0</v>
-      </c>
-      <c r="Q17">
-        <f>[2]results!AT6</f>
-        <v>0</v>
-      </c>
-      <c r="R17">
-        <f>[2]results!AU6</f>
-        <v>73.459999999999994</v>
-      </c>
-      <c r="S17">
-        <f>[2]results!AV6</f>
-        <v>0</v>
-      </c>
-      <c r="T17">
-        <f>[2]results!AW6</f>
-        <v>0</v>
-      </c>
-      <c r="U17">
-        <f>[2]results!AX6</f>
-        <v>0</v>
-      </c>
-      <c r="V17">
-        <f>[2]results!AY6</f>
-        <v>0</v>
-      </c>
-      <c r="W17">
-        <f>[2]results!AZ6</f>
-        <v>100.00999999999999</v>
-      </c>
-      <c r="Y17" t="str">
-        <f>[3]results!AQ6</f>
-        <v>minEQ&amp;HH</v>
-      </c>
-      <c r="Z17">
-        <f>[3]results!AR6</f>
-        <v>0</v>
-      </c>
-      <c r="AA17">
-        <f>[3]results!AS6</f>
-        <v>0</v>
-      </c>
-      <c r="AB17">
-        <f>[3]results!AT6</f>
-        <v>0</v>
-      </c>
-      <c r="AC17">
-        <f>[3]results!AU6</f>
-        <v>0</v>
-      </c>
-      <c r="AD17">
-        <f>[3]results!AV6</f>
-        <v>0</v>
-      </c>
-      <c r="AE17">
-        <f>[3]results!AW6</f>
-        <v>0</v>
-      </c>
-      <c r="AF17">
-        <f>[3]results!AX6</f>
-        <v>0</v>
-      </c>
-      <c r="AG17">
-        <f>[3]results!AY6</f>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="18" spans="1:33" x14ac:dyDescent="0.35">
-      <c r="B18">
-        <v>0.5</v>
-      </c>
-      <c r="C18">
-        <f t="shared" ref="C18:J18" si="7">Z17</f>
-        <v>0</v>
-      </c>
-      <c r="D18">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="E18">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F18">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="G18">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="H18">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="I18">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J18">
-        <f t="shared" si="7"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="20" spans="1:33" x14ac:dyDescent="0.35">
-      <c r="B20">
-        <v>-0.5</v>
-      </c>
-      <c r="C20">
-        <f t="shared" ref="C20:K20" si="8">O21</f>
-        <v>26.550000000000004</v>
-      </c>
-      <c r="D20">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="E20">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="F20">
-        <f t="shared" si="8"/>
-        <v>73.459999999999994</v>
-      </c>
-      <c r="G20">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="H20">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="I20">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="J20">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K20">
-        <f t="shared" si="8"/>
-        <v>100.00999999999999</v>
-      </c>
-    </row>
-    <row r="21" spans="1:33" x14ac:dyDescent="0.35">
-      <c r="A21" t="str">
-        <f>[1]results!AQ7</f>
-        <v>minCO2&amp;EQ</v>
-      </c>
-      <c r="C21">
-        <f>[1]results!AR7</f>
-        <v>1.29</v>
-      </c>
-      <c r="D21">
-        <f>[1]results!AS7</f>
-        <v>0</v>
-      </c>
-      <c r="E21">
-        <f>[1]results!AT7</f>
-        <v>0</v>
-      </c>
-      <c r="F21">
-        <f>[1]results!AU7</f>
-        <v>0</v>
-      </c>
-      <c r="G21">
-        <f>[1]results!AV7</f>
-        <v>0</v>
-      </c>
-      <c r="H21">
-        <f>[1]results!AW7</f>
-        <v>0</v>
-      </c>
-      <c r="I21">
-        <f>[1]results!AX7</f>
-        <v>0</v>
-      </c>
-      <c r="J21">
-        <f>[1]results!AY7</f>
-        <v>98.71</v>
-      </c>
-      <c r="K21">
-        <f>[1]results!AZ7</f>
-        <v>100</v>
-      </c>
-      <c r="N21" t="str">
-        <f>[2]results!AQ7</f>
-        <v>minCO2&amp;EQ</v>
-      </c>
-      <c r="O21">
-        <f>[2]results!AR7</f>
-        <v>26.550000000000004</v>
-      </c>
-      <c r="P21">
-        <f>[2]results!AS7</f>
-        <v>0</v>
-      </c>
-      <c r="Q21">
-        <f>[2]results!AT7</f>
-        <v>0</v>
-      </c>
-      <c r="R21">
-        <f>[2]results!AU7</f>
-        <v>73.459999999999994</v>
-      </c>
-      <c r="S21">
-        <f>[2]results!AV7</f>
-        <v>0</v>
-      </c>
-      <c r="T21">
-        <f>[2]results!AW7</f>
-        <v>0</v>
-      </c>
-      <c r="U21">
-        <f>[2]results!AX7</f>
-        <v>0</v>
-      </c>
-      <c r="V21">
-        <f>[2]results!AY7</f>
-        <v>0</v>
-      </c>
-      <c r="W21">
-        <f>[2]results!AZ7</f>
-        <v>100.00999999999999</v>
-      </c>
-      <c r="Y21" t="str">
-        <f>[3]results!AQ7</f>
-        <v>minCO2&amp;EQ</v>
-      </c>
-      <c r="Z21">
-        <f>[3]results!AR7</f>
-        <v>1.29</v>
-      </c>
-      <c r="AA21">
-        <f>[3]results!AS7</f>
-        <v>0</v>
-      </c>
-      <c r="AB21">
-        <f>[3]results!AT7</f>
-        <v>0</v>
-      </c>
-      <c r="AC21">
-        <f>[3]results!AU7</f>
-        <v>0</v>
-      </c>
-      <c r="AD21">
-        <f>[3]results!AV7</f>
-        <v>0</v>
-      </c>
-      <c r="AE21">
-        <f>[3]results!AW7</f>
-        <v>0</v>
-      </c>
-      <c r="AF21">
-        <f>[3]results!AX7</f>
-        <v>0</v>
-      </c>
-      <c r="AG21">
-        <f>[3]results!AY7</f>
-        <v>98.71</v>
-      </c>
-    </row>
-    <row r="22" spans="1:33" x14ac:dyDescent="0.35">
-      <c r="B22">
-        <v>0.5</v>
-      </c>
-      <c r="C22">
-        <f t="shared" ref="C22:J22" si="9">Z21</f>
-        <v>1.29</v>
-      </c>
-      <c r="D22">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="E22">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F22">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="G22">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H22">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="I22">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="J22">
-        <f t="shared" si="9"/>
-        <v>98.71</v>
-      </c>
-    </row>
-    <row r="24" spans="1:33" x14ac:dyDescent="0.35">
-      <c r="B24">
-        <v>-0.5</v>
-      </c>
-      <c r="C24">
-        <f t="shared" ref="C24:K24" si="10">O25</f>
-        <v>26.550000000000004</v>
-      </c>
-      <c r="D24">
-        <f t="shared" si="10"/>
-        <v>26.729999999999997</v>
-      </c>
-      <c r="E24">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="F24">
-        <f t="shared" si="10"/>
-        <v>46.73</v>
-      </c>
-      <c r="G24">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="H24">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="I24">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="J24">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="K24">
-        <f t="shared" si="10"/>
-        <v>100.00999999999999</v>
-      </c>
-    </row>
-    <row r="25" spans="1:33" x14ac:dyDescent="0.35">
-      <c r="A25" t="str">
-        <f>[1]results!AQ8</f>
-        <v>minCO2&amp;HH</v>
-      </c>
-      <c r="C25">
-        <f>[1]results!AR8</f>
-        <v>6.5</v>
-      </c>
-      <c r="D25">
-        <f>[1]results!AS8</f>
-        <v>0</v>
-      </c>
-      <c r="E25">
-        <f>[1]results!AT8</f>
-        <v>0</v>
-      </c>
-      <c r="F25">
-        <f>[1]results!AU8</f>
-        <v>0</v>
-      </c>
-      <c r="G25">
-        <f>[1]results!AV8</f>
-        <v>0</v>
-      </c>
-      <c r="H25">
-        <f>[1]results!AW8</f>
-        <v>0</v>
-      </c>
-      <c r="I25">
-        <f>[1]results!AX8</f>
-        <v>0</v>
-      </c>
-      <c r="J25">
-        <f>[1]results!AY8</f>
-        <v>93.51</v>
-      </c>
-      <c r="K25">
-        <f>[1]results!AZ8</f>
-        <v>100.01</v>
-      </c>
-      <c r="N25" t="str">
-        <f>[2]results!AQ8</f>
-        <v>minCO2&amp;HH</v>
-      </c>
-      <c r="O25">
-        <f>[2]results!AR8</f>
-        <v>26.550000000000004</v>
-      </c>
-      <c r="P25">
-        <f>[2]results!AS8</f>
-        <v>26.729999999999997</v>
-      </c>
-      <c r="Q25">
-        <f>[2]results!AT8</f>
-        <v>0</v>
-      </c>
-      <c r="R25">
-        <f>[2]results!AU8</f>
-        <v>46.73</v>
-      </c>
-      <c r="S25">
-        <f>[2]results!AV8</f>
-        <v>0</v>
-      </c>
-      <c r="T25">
-        <f>[2]results!AW8</f>
-        <v>0</v>
-      </c>
-      <c r="U25">
-        <f>[2]results!AX8</f>
-        <v>0</v>
-      </c>
-      <c r="V25">
-        <f>[2]results!AY8</f>
-        <v>0</v>
-      </c>
-      <c r="W25">
-        <f>[2]results!AZ8</f>
-        <v>100.00999999999999</v>
-      </c>
-      <c r="Y25" t="str">
-        <f>[3]results!AQ8</f>
-        <v>minCO2&amp;HH</v>
-      </c>
-      <c r="Z25">
-        <f>[3]results!AR8</f>
-        <v>8.86</v>
-      </c>
-      <c r="AA25">
-        <f>[3]results!AS8</f>
-        <v>0</v>
-      </c>
-      <c r="AB25">
-        <f>[3]results!AT8</f>
-        <v>0</v>
-      </c>
-      <c r="AC25">
-        <f>[3]results!AU8</f>
-        <v>0</v>
-      </c>
-      <c r="AD25">
-        <f>[3]results!AV8</f>
-        <v>0</v>
-      </c>
-      <c r="AE25">
-        <f>[3]results!AW8</f>
-        <v>0</v>
-      </c>
-      <c r="AF25">
-        <f>[3]results!AX8</f>
-        <v>0</v>
-      </c>
-      <c r="AG25">
-        <f>[3]results!AY8</f>
-        <v>91.15</v>
-      </c>
-    </row>
-    <row r="26" spans="1:33" x14ac:dyDescent="0.35">
-      <c r="B26">
-        <v>0.5</v>
-      </c>
-      <c r="C26">
-        <f t="shared" ref="C26:J26" si="11">Z25</f>
-        <v>8.86</v>
-      </c>
-      <c r="D26">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="E26">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="F26">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="G26">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="H26">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="I26">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="J26">
-        <f t="shared" si="11"/>
-        <v>91.15</v>
-      </c>
-    </row>
-    <row r="28" spans="1:33" x14ac:dyDescent="0.35">
-      <c r="B28">
-        <v>-0.5</v>
-      </c>
-      <c r="C28">
-        <f t="shared" ref="C28:K28" si="12">O29</f>
-        <v>26.550000000000004</v>
-      </c>
-      <c r="D28">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="E28">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="F28">
-        <f t="shared" si="12"/>
-        <v>73.459999999999994</v>
-      </c>
-      <c r="G28">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="H28">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="I28">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="J28">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="K28">
-        <f t="shared" si="12"/>
-        <v>100.00999999999999</v>
-      </c>
-    </row>
-    <row r="29" spans="1:33" x14ac:dyDescent="0.35">
-      <c r="A29" t="str">
-        <f>[1]results!AQ9</f>
-        <v>minCO2&amp;EQ&amp;HH</v>
-      </c>
-      <c r="C29">
-        <f>[1]results!AR9</f>
-        <v>1.29</v>
-      </c>
-      <c r="D29">
-        <f>[1]results!AS9</f>
-        <v>0</v>
-      </c>
-      <c r="E29">
-        <f>[1]results!AT9</f>
-        <v>0</v>
-      </c>
-      <c r="F29">
-        <f>[1]results!AU9</f>
-        <v>0</v>
-      </c>
-      <c r="G29">
-        <f>[1]results!AV9</f>
-        <v>0</v>
-      </c>
-      <c r="H29">
-        <f>[1]results!AW9</f>
-        <v>0</v>
-      </c>
-      <c r="I29">
-        <f>[1]results!AX9</f>
-        <v>0</v>
-      </c>
-      <c r="J29">
-        <f>[1]results!AY9</f>
-        <v>98.71</v>
-      </c>
-      <c r="K29">
-        <f>[1]results!AZ9</f>
-        <v>100</v>
-      </c>
-      <c r="N29" t="str">
-        <f>[2]results!AQ9</f>
-        <v>minCO2&amp;EQ&amp;HH</v>
-      </c>
-      <c r="O29">
-        <f>[2]results!AR9</f>
-        <v>26.550000000000004</v>
-      </c>
-      <c r="P29">
-        <f>[2]results!AS9</f>
-        <v>0</v>
-      </c>
-      <c r="Q29">
-        <f>[2]results!AT9</f>
-        <v>0</v>
-      </c>
-      <c r="R29">
-        <f>[2]results!AU9</f>
-        <v>73.459999999999994</v>
-      </c>
-      <c r="S29">
-        <f>[2]results!AV9</f>
-        <v>0</v>
-      </c>
-      <c r="T29">
-        <f>[2]results!AW9</f>
-        <v>0</v>
-      </c>
-      <c r="U29">
-        <f>[2]results!AX9</f>
-        <v>0</v>
-      </c>
-      <c r="V29">
-        <f>[2]results!AY9</f>
-        <v>0</v>
-      </c>
-      <c r="W29">
-        <f>[2]results!AZ9</f>
-        <v>100.00999999999999</v>
-      </c>
-      <c r="Y29" t="str">
-        <f>[3]results!AQ9</f>
-        <v>minCO2&amp;EQ&amp;HH</v>
-      </c>
-      <c r="Z29">
-        <f>[3]results!AR9</f>
-        <v>1.29</v>
-      </c>
-      <c r="AA29">
-        <f>[3]results!AS9</f>
-        <v>0</v>
-      </c>
-      <c r="AB29">
-        <f>[3]results!AT9</f>
-        <v>0</v>
-      </c>
-      <c r="AC29">
-        <f>[3]results!AU9</f>
-        <v>0</v>
-      </c>
-      <c r="AD29">
-        <f>[3]results!AV9</f>
-        <v>0</v>
-      </c>
-      <c r="AE29">
-        <f>[3]results!AW9</f>
-        <v>0</v>
-      </c>
-      <c r="AF29">
-        <f>[3]results!AX9</f>
-        <v>0</v>
-      </c>
-      <c r="AG29">
-        <f>[3]results!AY9</f>
-        <v>98.71</v>
-      </c>
-    </row>
-    <row r="30" spans="1:33" x14ac:dyDescent="0.35">
-      <c r="B30">
-        <v>0.5</v>
-      </c>
-      <c r="C30">
-        <f t="shared" ref="C30:J30" si="13">Z29</f>
-        <v>1.29</v>
-      </c>
-      <c r="D30">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="E30">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="F30">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="G30">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="H30">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="I30">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="J30">
-        <f t="shared" si="13"/>
         <v>98.71</v>
       </c>
     </row>
@@ -6221,7 +4497,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D929B012-5109-44C6-8E37-563FE0CBD43E}">
-  <dimension ref="A1:S29"/>
+  <dimension ref="A1:S13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.35">
@@ -6307,11 +4583,11 @@
     <row r="3" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B3">
         <f>H4</f>
-        <v>26.550000000000004</v>
+        <v>11.95</v>
       </c>
       <c r="C3">
         <f>I4</f>
-        <v>32.229999999999997</v>
+        <v>14.5</v>
       </c>
       <c r="D3">
         <f>J4</f>
@@ -6319,13 +4595,13 @@
       </c>
       <c r="E3">
         <f>K4</f>
-        <v>41.23</v>
+        <v>73.55</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A4" t="str">
         <f>[4]results!AJ3</f>
-        <v>minCO2</v>
+        <v>minCC</v>
       </c>
       <c r="B4">
         <f>[4]results!AK3</f>
@@ -6348,20 +4624,20 @@
         <v>minCO2</v>
       </c>
       <c r="H4">
-        <f>[5]results!AK3</f>
-        <v>26.550000000000004</v>
+        <f>[11]results!AK3</f>
+        <v>11.95</v>
       </c>
       <c r="I4">
-        <f>[5]results!AL3</f>
-        <v>32.229999999999997</v>
+        <f>[11]results!AL3</f>
+        <v>14.5</v>
       </c>
       <c r="J4">
-        <f>[5]results!AM3</f>
+        <f>[11]results!AM3</f>
         <v>0</v>
       </c>
       <c r="K4">
-        <f>[5]results!AN3</f>
-        <v>41.23</v>
+        <f>[11]results!AN3</f>
+        <v>73.55</v>
       </c>
       <c r="L4">
         <f>[5]results!AO3</f>
@@ -6372,20 +4648,20 @@
         <v>minCO2</v>
       </c>
       <c r="O4">
-        <f>[6]results!AK3</f>
-        <v>8.86</v>
+        <f>[10]results!AK3</f>
+        <v>14.61</v>
       </c>
       <c r="P4">
-        <f>[6]results!AL3</f>
-        <v>6.95</v>
+        <f>[10]results!AL3</f>
+        <v>17.72</v>
       </c>
       <c r="Q4">
-        <f>[6]results!AM3</f>
-        <v>32.25</v>
+        <f>[10]results!AM3</f>
+        <v>0</v>
       </c>
       <c r="R4">
-        <f>[6]results!AN3</f>
-        <v>51.95</v>
+        <f>[10]results!AN3</f>
+        <v>67.680000000000007</v>
       </c>
       <c r="S4">
         <f>[6]results!AO3</f>
@@ -6395,25 +4671,25 @@
     <row r="5" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B5">
         <f>O4</f>
-        <v>8.86</v>
+        <v>14.61</v>
       </c>
       <c r="C5">
         <f>P4</f>
-        <v>6.95</v>
+        <v>17.72</v>
       </c>
       <c r="D5">
         <f>Q4</f>
-        <v>32.25</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <f>R4</f>
-        <v>51.95</v>
+        <v>67.680000000000007</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B7">
         <f>H8</f>
-        <v>26.550000000000004</v>
+        <v>11.95</v>
       </c>
       <c r="C7">
         <f>I8</f>
@@ -6421,7 +4697,7 @@
       </c>
       <c r="D7">
         <f>J8</f>
-        <v>73.459999999999994</v>
+        <v>88.06</v>
       </c>
       <c r="E7">
         <f>K8</f>
@@ -6454,19 +4730,19 @@
         <v>minEQ</v>
       </c>
       <c r="H8">
-        <f>[5]results!AK4</f>
-        <v>26.550000000000004</v>
+        <f>[11]results!AK4</f>
+        <v>11.95</v>
       </c>
       <c r="I8">
-        <f>[5]results!AL4</f>
+        <f>[11]results!AL4</f>
         <v>0</v>
       </c>
       <c r="J8">
-        <f>[5]results!AM4</f>
-        <v>73.459999999999994</v>
+        <f>[11]results!AM4</f>
+        <v>88.06</v>
       </c>
       <c r="K8">
-        <f>[5]results!AN4</f>
+        <f>[11]results!AN4</f>
         <v>0</v>
       </c>
       <c r="L8">
@@ -6478,20 +4754,20 @@
         <v>minEQ</v>
       </c>
       <c r="O8">
-        <f>[6]results!AK4</f>
-        <v>8.86</v>
+        <f>[10]results!AK4</f>
+        <v>14.61</v>
       </c>
       <c r="P8">
-        <f>[6]results!AL4</f>
-        <v>3.41</v>
+        <f>[10]results!AL4</f>
+        <v>0</v>
       </c>
       <c r="Q8">
-        <f>[6]results!AM4</f>
-        <v>62.34</v>
+        <f>[10]results!AM4</f>
+        <v>85.4</v>
       </c>
       <c r="R8">
-        <f>[6]results!AN4</f>
-        <v>25.4</v>
+        <f>[10]results!AN4</f>
+        <v>0</v>
       </c>
       <c r="S8">
         <f>[6]results!AO4</f>
@@ -6501,25 +4777,25 @@
     <row r="9" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B9">
         <f>O8</f>
-        <v>8.86</v>
+        <v>14.61</v>
       </c>
       <c r="C9">
         <f>P8</f>
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="D9">
         <f>Q8</f>
-        <v>62.34</v>
+        <v>85.4</v>
       </c>
       <c r="E9">
         <f>R8</f>
-        <v>25.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B11">
         <f>H12</f>
-        <v>26.550000000000004</v>
+        <v>11.95</v>
       </c>
       <c r="C11">
         <f>I12</f>
@@ -6527,7 +4803,7 @@
       </c>
       <c r="D11">
         <f>J12</f>
-        <v>73.459999999999994</v>
+        <v>88.06</v>
       </c>
       <c r="E11">
         <f>K12</f>
@@ -6560,19 +4836,19 @@
         <v>minHH</v>
       </c>
       <c r="H12">
-        <f>[5]results!AK5</f>
-        <v>26.550000000000004</v>
+        <f>[11]results!AK5</f>
+        <v>11.95</v>
       </c>
       <c r="I12">
-        <f>[5]results!AL5</f>
+        <f>[11]results!AL5</f>
         <v>0</v>
       </c>
       <c r="J12">
-        <f>[5]results!AM5</f>
-        <v>73.459999999999994</v>
+        <f>[11]results!AM5</f>
+        <v>88.06</v>
       </c>
       <c r="K12">
-        <f>[5]results!AN5</f>
+        <f>[11]results!AN5</f>
         <v>0</v>
       </c>
       <c r="L12">
@@ -6584,20 +4860,20 @@
         <v>minHH</v>
       </c>
       <c r="O12">
-        <f>[6]results!AK5</f>
-        <v>8.86</v>
+        <f>[10]results!AK5</f>
+        <v>14.61</v>
       </c>
       <c r="P12">
-        <f>[6]results!AL5</f>
-        <v>3.41</v>
+        <f>[10]results!AL5</f>
+        <v>0</v>
       </c>
       <c r="Q12">
-        <f>[6]results!AM5</f>
-        <v>62.34</v>
+        <f>[10]results!AM5</f>
+        <v>85.4</v>
       </c>
       <c r="R12">
-        <f>[6]results!AN5</f>
-        <v>25.4</v>
+        <f>[10]results!AN5</f>
+        <v>0</v>
       </c>
       <c r="S12">
         <f>[6]results!AO5</f>
@@ -6607,443 +4883,19 @@
     <row r="13" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B13">
         <f>O12</f>
-        <v>8.86</v>
+        <v>14.61</v>
       </c>
       <c r="C13">
         <f>P12</f>
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="D13">
         <f>Q12</f>
-        <v>62.34</v>
+        <v>85.4</v>
       </c>
       <c r="E13">
         <f>R12</f>
-        <v>25.4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="B15">
-        <f>H16</f>
-        <v>26.550000000000004</v>
-      </c>
-      <c r="C15">
-        <f>I16</f>
-        <v>0</v>
-      </c>
-      <c r="D15">
-        <f>J16</f>
-        <v>73.459999999999994</v>
-      </c>
-      <c r="E15">
-        <f>K16</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A16" t="str">
-        <f>[4]results!AJ6</f>
-        <v>minEQ&amp;HH</v>
-      </c>
-      <c r="B16">
-        <f>[4]results!AK6</f>
-        <v>13.280000000000001</v>
-      </c>
-      <c r="C16">
-        <f>[4]results!AL6</f>
-        <v>0</v>
-      </c>
-      <c r="D16">
-        <f>[4]results!AM6</f>
-        <v>86.73</v>
-      </c>
-      <c r="E16">
-        <f>[4]results!AN6</f>
-        <v>0</v>
-      </c>
-      <c r="G16" t="str">
-        <f>[5]results!AJ6</f>
-        <v>minEQ&amp;HH</v>
-      </c>
-      <c r="H16">
-        <f>[5]results!AK6</f>
-        <v>26.550000000000004</v>
-      </c>
-      <c r="I16">
-        <f>[5]results!AL6</f>
-        <v>0</v>
-      </c>
-      <c r="J16">
-        <f>[5]results!AM6</f>
-        <v>73.459999999999994</v>
-      </c>
-      <c r="K16">
-        <f>[5]results!AN6</f>
-        <v>0</v>
-      </c>
-      <c r="L16">
-        <f>[5]results!AO6</f>
-        <v>100.00999999999999</v>
-      </c>
-      <c r="N16" t="str">
-        <f>[6]results!AJ6</f>
-        <v>minEQ&amp;HH</v>
-      </c>
-      <c r="O16">
-        <f>[6]results!AK6</f>
-        <v>8.86</v>
-      </c>
-      <c r="P16">
-        <f>[6]results!AL6</f>
-        <v>3.41</v>
-      </c>
-      <c r="Q16">
-        <f>[6]results!AM6</f>
-        <v>62.34</v>
-      </c>
-      <c r="R16">
-        <f>[6]results!AN6</f>
-        <v>25.4</v>
-      </c>
-      <c r="S16">
-        <f>[6]results!AO6</f>
-        <v>100.00999999999999</v>
-      </c>
-    </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="B17">
-        <f>O16</f>
-        <v>8.86</v>
-      </c>
-      <c r="C17">
-        <f>P16</f>
-        <v>3.41</v>
-      </c>
-      <c r="D17">
-        <f>Q16</f>
-        <v>62.34</v>
-      </c>
-      <c r="E17">
-        <f>R16</f>
-        <v>25.4</v>
-      </c>
-    </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="B19">
-        <f>H20</f>
-        <v>26.550000000000004</v>
-      </c>
-      <c r="C19">
-        <f>I20</f>
-        <v>0</v>
-      </c>
-      <c r="D19">
-        <f>J20</f>
-        <v>73.459999999999994</v>
-      </c>
-      <c r="E19">
-        <f>K20</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A20" t="str">
-        <f>[4]results!AJ7</f>
-        <v>minCO2&amp;EQ</v>
-      </c>
-      <c r="B20">
-        <f>[4]results!AK7</f>
-        <v>13.280000000000001</v>
-      </c>
-      <c r="C20">
-        <f>[4]results!AL7</f>
-        <v>0</v>
-      </c>
-      <c r="D20">
-        <f>[4]results!AM7</f>
-        <v>86.73</v>
-      </c>
-      <c r="E20">
-        <f>[4]results!AN7</f>
-        <v>0</v>
-      </c>
-      <c r="G20" t="str">
-        <f>[5]results!AJ7</f>
-        <v>minCO2&amp;EQ</v>
-      </c>
-      <c r="H20">
-        <f>[5]results!AK7</f>
-        <v>26.550000000000004</v>
-      </c>
-      <c r="I20">
-        <f>[5]results!AL7</f>
-        <v>0</v>
-      </c>
-      <c r="J20">
-        <f>[5]results!AM7</f>
-        <v>73.459999999999994</v>
-      </c>
-      <c r="K20">
-        <f>[5]results!AN7</f>
-        <v>0</v>
-      </c>
-      <c r="L20">
-        <f>[5]results!AO7</f>
-        <v>100.00999999999999</v>
-      </c>
-      <c r="N20" t="str">
-        <f>[6]results!AJ7</f>
-        <v>minCO2&amp;EQ</v>
-      </c>
-      <c r="O20">
-        <f>[6]results!AK7</f>
-        <v>8.86</v>
-      </c>
-      <c r="P20">
-        <f>[6]results!AL7</f>
-        <v>3.41</v>
-      </c>
-      <c r="Q20">
-        <f>[6]results!AM7</f>
-        <v>62.34</v>
-      </c>
-      <c r="R20">
-        <f>[6]results!AN7</f>
-        <v>25.4</v>
-      </c>
-      <c r="S20">
-        <f>[6]results!AO7</f>
-        <v>100.00999999999999</v>
-      </c>
-    </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="B21">
-        <f>O20</f>
-        <v>8.86</v>
-      </c>
-      <c r="C21">
-        <f>P20</f>
-        <v>3.41</v>
-      </c>
-      <c r="D21">
-        <f>Q20</f>
-        <v>62.34</v>
-      </c>
-      <c r="E21">
-        <f>R20</f>
-        <v>25.4</v>
-      </c>
-    </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="B23">
-        <f>H24</f>
-        <v>26.550000000000004</v>
-      </c>
-      <c r="C23">
-        <f>I24</f>
-        <v>26.729999999999997</v>
-      </c>
-      <c r="D23">
-        <f>J24</f>
-        <v>46.73</v>
-      </c>
-      <c r="E23">
-        <f>K24</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A24" t="str">
-        <f>[4]results!AJ8</f>
-        <v>minCO2&amp;HH</v>
-      </c>
-      <c r="B24">
-        <f>[4]results!AK8</f>
-        <v>13.280000000000001</v>
-      </c>
-      <c r="C24">
-        <f>[4]results!AL8</f>
-        <v>6.6999999999999993</v>
-      </c>
-      <c r="D24">
-        <f>[4]results!AM8</f>
-        <v>80.03</v>
-      </c>
-      <c r="E24">
-        <f>[4]results!AN8</f>
-        <v>0</v>
-      </c>
-      <c r="G24" t="str">
-        <f>[5]results!AJ8</f>
-        <v>minCO2&amp;HH</v>
-      </c>
-      <c r="H24">
-        <f>[5]results!AK8</f>
-        <v>26.550000000000004</v>
-      </c>
-      <c r="I24">
-        <f>[5]results!AL8</f>
-        <v>26.729999999999997</v>
-      </c>
-      <c r="J24">
-        <f>[5]results!AM8</f>
-        <v>46.73</v>
-      </c>
-      <c r="K24">
-        <f>[5]results!AN8</f>
-        <v>0</v>
-      </c>
-      <c r="L24">
-        <f>[5]results!AO8</f>
-        <v>100.00999999999999</v>
-      </c>
-      <c r="N24" t="str">
-        <f>[6]results!AJ8</f>
-        <v>minCO2&amp;HH</v>
-      </c>
-      <c r="O24">
-        <f>[6]results!AK8</f>
-        <v>8.86</v>
-      </c>
-      <c r="P24">
-        <f>[6]results!AL8</f>
-        <v>3.41</v>
-      </c>
-      <c r="Q24">
-        <f>[6]results!AM8</f>
-        <v>62.34</v>
-      </c>
-      <c r="R24">
-        <f>[6]results!AN8</f>
-        <v>25.4</v>
-      </c>
-      <c r="S24">
-        <f>[6]results!AO8</f>
-        <v>100.00999999999999</v>
-      </c>
-    </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="B25">
-        <f t="shared" ref="B25:E25" si="0">O24</f>
-        <v>8.86</v>
-      </c>
-      <c r="C25">
-        <f t="shared" si="0"/>
-        <v>3.41</v>
-      </c>
-      <c r="D25">
-        <f t="shared" si="0"/>
-        <v>62.34</v>
-      </c>
-      <c r="E25">
-        <f t="shared" si="0"/>
-        <v>25.4</v>
-      </c>
-    </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="B27">
-        <f>H28</f>
-        <v>26.550000000000004</v>
-      </c>
-      <c r="C27">
-        <f>I28</f>
-        <v>0</v>
-      </c>
-      <c r="D27">
-        <f>J28</f>
-        <v>73.459999999999994</v>
-      </c>
-      <c r="E27">
-        <f>K28</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A28" t="str">
-        <f>[4]results!AJ9</f>
-        <v>minCO2&amp;EQ&amp;HH</v>
-      </c>
-      <c r="B28">
-        <f>[4]results!AK9</f>
-        <v>13.280000000000001</v>
-      </c>
-      <c r="C28">
-        <f>[4]results!AL9</f>
-        <v>0</v>
-      </c>
-      <c r="D28">
-        <f>[4]results!AM9</f>
-        <v>86.73</v>
-      </c>
-      <c r="E28">
-        <f>[4]results!AN9</f>
-        <v>0</v>
-      </c>
-      <c r="G28" t="str">
-        <f>[5]results!AJ9</f>
-        <v>minCO2&amp;EQ&amp;HH</v>
-      </c>
-      <c r="H28">
-        <f>[5]results!AK9</f>
-        <v>26.550000000000004</v>
-      </c>
-      <c r="I28">
-        <f>[5]results!AL9</f>
-        <v>0</v>
-      </c>
-      <c r="J28">
-        <f>[5]results!AM9</f>
-        <v>73.459999999999994</v>
-      </c>
-      <c r="K28">
-        <f>[5]results!AN9</f>
-        <v>0</v>
-      </c>
-      <c r="L28">
-        <f>[5]results!AO9</f>
-        <v>100.00999999999999</v>
-      </c>
-      <c r="N28" t="str">
-        <f>[6]results!AJ9</f>
-        <v>minCO2&amp;EQ&amp;HH</v>
-      </c>
-      <c r="O28">
-        <f>[6]results!AK9</f>
-        <v>8.86</v>
-      </c>
-      <c r="P28">
-        <f>[6]results!AL9</f>
-        <v>3.41</v>
-      </c>
-      <c r="Q28">
-        <f>[6]results!AM9</f>
-        <v>62.34</v>
-      </c>
-      <c r="R28">
-        <f>[6]results!AN9</f>
-        <v>25.4</v>
-      </c>
-      <c r="S28">
-        <f>[6]results!AO9</f>
-        <v>100.00999999999999</v>
-      </c>
-    </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="B29">
-        <f>O28</f>
-        <v>8.86</v>
-      </c>
-      <c r="C29">
-        <f>P28</f>
-        <v>3.41</v>
-      </c>
-      <c r="D29">
-        <f>Q28</f>
-        <v>62.34</v>
-      </c>
-      <c r="E29">
-        <f>R28</f>
-        <v>25.4</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/simulations/correction_peat_market/AS_marché/AS_marché_hobby/AS_resume_hobby.xlsx
+++ b/simulations/correction_peat_market/AS_marché/AS_marché_hobby/AS_resume_hobby.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\hravoaha\Desktop\Thèse\Thèse 2023\Objectif 2\biowaste_optim\simulations\correction_peat_market\AS_marché\AS_marché_hobby\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A426642-21AB-4AB9-9F9A-150770E766E0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10CE4149-8174-44FF-A7E8-E6BA919836AA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="inv" sheetId="1" r:id="rId1"/>
@@ -267,7 +267,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>6.5</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>6.5</c:v>
@@ -285,7 +285,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.29</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>1.29</c:v>
@@ -601,7 +601,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>93.51</c:v>
+                  <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>93.51</c:v>
@@ -755,7 +755,7 @@
                   <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>98.71</c:v>
+                  <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>98.71</c:v>
@@ -1108,31 +1108,31 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>11.95</c:v>
+                  <c:v>2.66</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>13.280000000000001</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>14.61</c:v>
+                  <c:v>23.900000000000002</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>11.95</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>13.280000000000001</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>14.61</c:v>
+                  <c:v>23.900000000000002</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>11.95</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>13.280000000000001</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>14.61</c:v>
+                  <c:v>23.900000000000002</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1174,13 +1174,13 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>14.5</c:v>
+                  <c:v>1.06</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>16.11</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>17.72</c:v>
+                  <c:v>29</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>0</c:v>
@@ -1240,7 +1240,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>18.36</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
@@ -1249,22 +1249,22 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>88.06</c:v>
+                  <c:v>93.51</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>86.73</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>85.4</c:v>
+                  <c:v>76.11</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>88.06</c:v>
+                  <c:v>87.36</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>86.73</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>85.4</c:v>
+                  <c:v>76.11</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1306,16 +1306,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>73.55</c:v>
+                  <c:v>77.930000000000007</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>70.62</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>67.680000000000007</c:v>
+                  <c:v>47.11</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>6.49</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0</c:v>
@@ -1324,7 +1324,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0</c:v>
+                  <c:v>12.64</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>0</c:v>
@@ -2682,16 +2682,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>430212</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>265112</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>457200</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>139700</xdr:rowOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>295275</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -2794,113 +2794,229 @@
 
 <file path=xl/externalLinks/externalLink10.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="results"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="3">
-          <cell r="AK3">
-            <v>14.61</v>
-          </cell>
-          <cell r="AL3">
-            <v>17.72</v>
-          </cell>
-          <cell r="AM3">
-            <v>0</v>
-          </cell>
-          <cell r="AN3">
-            <v>67.680000000000007</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="AK4">
-            <v>14.61</v>
-          </cell>
-          <cell r="AL4">
-            <v>0</v>
-          </cell>
-          <cell r="AM4">
-            <v>85.4</v>
-          </cell>
-          <cell r="AN4">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="AK5">
-            <v>14.61</v>
-          </cell>
-          <cell r="AL5">
-            <v>0</v>
-          </cell>
-          <cell r="AM5">
-            <v>85.4</v>
-          </cell>
-          <cell r="AN5">
-            <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
+  <oleLink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" progId="Excel.Sheet.12">
+    <oleItems>
+      <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+        <mc:Choice Requires="x14">
+          <x14:oleItem name="!results!L3C44:L3C51" advise="1">
+            <x14:values cols="8">
+              <value>
+                <val>0</val>
+              </value>
+              <value>
+                <val>0</val>
+              </value>
+              <value>
+                <val>0</val>
+              </value>
+              <value>
+                <val>0</val>
+              </value>
+              <value>
+                <val>0</val>
+              </value>
+              <value>
+                <val>100</val>
+              </value>
+              <value>
+                <val>0</val>
+              </value>
+              <value>
+                <val>0</val>
+              </value>
+            </x14:values>
+          </x14:oleItem>
+        </mc:Choice>
+        <mc:Fallback>
+          <oleItem name="!results!L3C44:L3C51" advise="1"/>
+        </mc:Fallback>
+      </mc:AlternateContent>
+      <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+        <mc:Choice Requires="x14">
+          <x14:oleItem name="!results!L4C44:L4C51" advise="1">
+            <x14:values cols="8">
+              <value>
+                <val>0</val>
+              </value>
+              <value>
+                <val>0</val>
+              </value>
+              <value>
+                <val>0</val>
+              </value>
+              <value>
+                <val>0</val>
+              </value>
+              <value>
+                <val>0</val>
+              </value>
+              <value>
+                <val>0</val>
+              </value>
+              <value>
+                <val>0</val>
+              </value>
+              <value>
+                <val>100</val>
+              </value>
+            </x14:values>
+          </x14:oleItem>
+        </mc:Choice>
+        <mc:Fallback>
+          <oleItem name="!results!L4C44:L4C51" advise="1"/>
+        </mc:Fallback>
+      </mc:AlternateContent>
+      <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+        <mc:Choice Requires="x14">
+          <x14:oleItem name="!results!L5C44:L5C51" advise="1">
+            <x14:values cols="8">
+              <value>
+                <val>0</val>
+              </value>
+              <value>
+                <val>0</val>
+              </value>
+              <value>
+                <val>0</val>
+              </value>
+              <value>
+                <val>0</val>
+              </value>
+              <value>
+                <val>0</val>
+              </value>
+              <value>
+                <val>0</val>
+              </value>
+              <value>
+                <val>0</val>
+              </value>
+              <value>
+                <val>100</val>
+              </value>
+            </x14:values>
+          </x14:oleItem>
+        </mc:Choice>
+        <mc:Fallback>
+          <oleItem name="!results!L5C44:L5C51" advise="1"/>
+        </mc:Fallback>
+      </mc:AlternateContent>
+    </oleItems>
+  </oleLink>
 </externalLink>
 </file>
 
 <file path=xl/externalLinks/externalLink11.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="results"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="3">
-          <cell r="AK3">
-            <v>11.95</v>
-          </cell>
-          <cell r="AL3">
-            <v>14.5</v>
-          </cell>
-          <cell r="AM3">
-            <v>0</v>
-          </cell>
-          <cell r="AN3">
-            <v>73.55</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="AK4">
-            <v>11.95</v>
-          </cell>
-          <cell r="AL4">
-            <v>0</v>
-          </cell>
-          <cell r="AM4">
-            <v>88.06</v>
-          </cell>
-          <cell r="AN4">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="AK5">
-            <v>11.95</v>
-          </cell>
-          <cell r="AL5">
-            <v>0</v>
-          </cell>
-          <cell r="AM5">
-            <v>88.06</v>
-          </cell>
-          <cell r="AN5">
-            <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
+  <oleLink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" progId="Excel.Sheet.12">
+    <oleItems>
+      <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+        <mc:Choice Requires="x14">
+          <x14:oleItem name="!results!L3C44:L3C51" advise="1">
+            <x14:values cols="8">
+              <value>
+                <val>6.5</val>
+              </value>
+              <value>
+                <val>0</val>
+              </value>
+              <value>
+                <val>0</val>
+              </value>
+              <value>
+                <val>0</val>
+              </value>
+              <value>
+                <val>0</val>
+              </value>
+              <value>
+                <val>93.51</val>
+              </value>
+              <value>
+                <val>0</val>
+              </value>
+              <value>
+                <val>0</val>
+              </value>
+            </x14:values>
+          </x14:oleItem>
+        </mc:Choice>
+        <mc:Fallback>
+          <oleItem name="!results!L3C44:L3C51" advise="1"/>
+        </mc:Fallback>
+      </mc:AlternateContent>
+      <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+        <mc:Choice Requires="x14">
+          <x14:oleItem name="!results!L4C44:L4C51" advise="1">
+            <x14:values cols="8">
+              <value>
+                <val>0</val>
+              </value>
+              <value>
+                <val>0</val>
+              </value>
+              <value>
+                <val>0</val>
+              </value>
+              <value>
+                <val>0</val>
+              </value>
+              <value>
+                <val>0</val>
+              </value>
+              <value>
+                <val>0</val>
+              </value>
+              <value>
+                <val>0</val>
+              </value>
+              <value>
+                <val>100</val>
+              </value>
+            </x14:values>
+          </x14:oleItem>
+        </mc:Choice>
+        <mc:Fallback>
+          <oleItem name="!results!L4C44:L4C51" advise="1"/>
+        </mc:Fallback>
+      </mc:AlternateContent>
+      <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+        <mc:Choice Requires="x14">
+          <x14:oleItem name="!results!L5C44:L5C51" advise="1">
+            <x14:values cols="8">
+              <value>
+                <val>1.29</val>
+              </value>
+              <value>
+                <val>0</val>
+              </value>
+              <value>
+                <val>0</val>
+              </value>
+              <value>
+                <val>0</val>
+              </value>
+              <value>
+                <val>0</val>
+              </value>
+              <value>
+                <val>0</val>
+              </value>
+              <value>
+                <val>0</val>
+              </value>
+              <value>
+                <val>98.71</val>
+              </value>
+            </x14:values>
+          </x14:oleItem>
+        </mc:Choice>
+        <mc:Fallback>
+          <oleItem name="!results!L5C44:L5C51" advise="1"/>
+        </mc:Fallback>
+      </mc:AlternateContent>
+    </oleItems>
+  </oleLink>
 </externalLink>
 </file>
 
@@ -3033,6 +3149,101 @@
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
+      <sheetName val="results"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="3">
+          <cell r="AK3">
+            <v>-651101.69874275697</v>
+          </cell>
+          <cell r="AR3">
+            <v>6.5</v>
+          </cell>
+          <cell r="AS3">
+            <v>0</v>
+          </cell>
+          <cell r="AT3">
+            <v>0</v>
+          </cell>
+          <cell r="AU3">
+            <v>0</v>
+          </cell>
+          <cell r="AV3">
+            <v>0</v>
+          </cell>
+          <cell r="AW3">
+            <v>93.51</v>
+          </cell>
+          <cell r="AX3">
+            <v>0</v>
+          </cell>
+          <cell r="AY3">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="AR4">
+            <v>0</v>
+          </cell>
+          <cell r="AS4">
+            <v>0</v>
+          </cell>
+          <cell r="AT4">
+            <v>0</v>
+          </cell>
+          <cell r="AU4">
+            <v>0</v>
+          </cell>
+          <cell r="AV4">
+            <v>0</v>
+          </cell>
+          <cell r="AW4">
+            <v>0</v>
+          </cell>
+          <cell r="AX4">
+            <v>0</v>
+          </cell>
+          <cell r="AY4">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="AR5">
+            <v>1.29</v>
+          </cell>
+          <cell r="AS5">
+            <v>0</v>
+          </cell>
+          <cell r="AT5">
+            <v>0</v>
+          </cell>
+          <cell r="AU5">
+            <v>0</v>
+          </cell>
+          <cell r="AV5">
+            <v>0</v>
+          </cell>
+          <cell r="AW5">
+            <v>0</v>
+          </cell>
+          <cell r="AX5">
+            <v>0</v>
+          </cell>
+          <cell r="AY5">
+            <v>98.71</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
       <sheetName val="Contrainte de capacité"/>
       <sheetName val="results"/>
       <sheetName val="Feuil1"/>
@@ -3108,59 +3319,10 @@
         </row>
       </sheetData>
       <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="results"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="AJ2" t="str">
-            <v>name</v>
-          </cell>
-          <cell r="AK2" t="str">
-            <v>HC</v>
-          </cell>
-          <cell r="AL2" t="str">
-            <v>IC</v>
-          </cell>
-          <cell r="AM2" t="str">
-            <v>AD-cog-comp</v>
-          </cell>
-          <cell r="AN2" t="str">
-            <v>AD-biomet-dig</v>
-          </cell>
-        </row>
+      <sheetData sheetId="3">
         <row r="3">
-          <cell r="AJ3" t="str">
-            <v>minCO2</v>
-          </cell>
-          <cell r="AO3">
-            <v>100.00999999999999</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="AJ4" t="str">
-            <v>minEQ</v>
-          </cell>
-          <cell r="AO4">
-            <v>100.00999999999999</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="AJ5" t="str">
-            <v>minHH</v>
-          </cell>
-          <cell r="AO5">
-            <v>100.00999999999999</v>
+          <cell r="B3">
+            <v>-405095.98916297092</v>
           </cell>
         </row>
       </sheetData>
@@ -3199,15 +3361,12 @@
             <v>minCO2</v>
           </cell>
           <cell r="AO3">
-            <v>100.01</v>
+            <v>100.00999999999999</v>
           </cell>
         </row>
         <row r="4">
           <cell r="AJ4" t="str">
             <v>minEQ</v>
-          </cell>
-          <cell r="AO4">
-            <v>100.00999999999999</v>
           </cell>
         </row>
         <row r="5">
@@ -3232,82 +3391,45 @@
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
+        <row r="2">
+          <cell r="AJ2" t="str">
+            <v>name</v>
+          </cell>
+          <cell r="AK2" t="str">
+            <v>HC</v>
+          </cell>
+          <cell r="AL2" t="str">
+            <v>IC</v>
+          </cell>
+          <cell r="AM2" t="str">
+            <v>AD-cog-comp</v>
+          </cell>
+          <cell r="AN2" t="str">
+            <v>AD-biomet-dig</v>
+          </cell>
+        </row>
         <row r="3">
-          <cell r="AR3">
-            <v>6.5</v>
-          </cell>
-          <cell r="AS3">
-            <v>0</v>
-          </cell>
-          <cell r="AT3">
-            <v>0</v>
-          </cell>
-          <cell r="AU3">
-            <v>0</v>
-          </cell>
-          <cell r="AV3">
-            <v>0</v>
-          </cell>
-          <cell r="AW3">
-            <v>93.51</v>
-          </cell>
-          <cell r="AX3">
-            <v>0</v>
-          </cell>
-          <cell r="AY3">
-            <v>0</v>
+          <cell r="AJ3" t="str">
+            <v>minCO2</v>
+          </cell>
+          <cell r="AO3">
+            <v>100.01</v>
           </cell>
         </row>
         <row r="4">
-          <cell r="AR4">
-            <v>0</v>
-          </cell>
-          <cell r="AS4">
-            <v>0</v>
-          </cell>
-          <cell r="AT4">
-            <v>0</v>
-          </cell>
-          <cell r="AU4">
-            <v>0</v>
-          </cell>
-          <cell r="AV4">
-            <v>0</v>
-          </cell>
-          <cell r="AW4">
-            <v>0</v>
-          </cell>
-          <cell r="AX4">
-            <v>0</v>
-          </cell>
-          <cell r="AY4">
-            <v>100</v>
+          <cell r="AJ4" t="str">
+            <v>minEQ</v>
+          </cell>
+          <cell r="AO4">
+            <v>100.00999999999999</v>
           </cell>
         </row>
         <row r="5">
-          <cell r="AR5">
-            <v>1.29</v>
-          </cell>
-          <cell r="AS5">
-            <v>0</v>
-          </cell>
-          <cell r="AT5">
-            <v>0</v>
-          </cell>
-          <cell r="AU5">
-            <v>0</v>
-          </cell>
-          <cell r="AV5">
-            <v>0</v>
-          </cell>
-          <cell r="AW5">
-            <v>0</v>
-          </cell>
-          <cell r="AX5">
-            <v>0</v>
-          </cell>
-          <cell r="AY5">
-            <v>98.71</v>
+          <cell r="AJ5" t="str">
+            <v>minHH</v>
+          </cell>
+          <cell r="AO5">
+            <v>100.00999999999999</v>
           </cell>
         </row>
       </sheetData>
@@ -3318,185 +3440,157 @@
 
 <file path=xl/externalLinks/externalLink8.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="results"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="3">
-          <cell r="AR3">
-            <v>6.5</v>
-          </cell>
-          <cell r="AS3">
-            <v>0</v>
-          </cell>
-          <cell r="AT3">
-            <v>0</v>
-          </cell>
-          <cell r="AU3">
-            <v>0</v>
-          </cell>
-          <cell r="AV3">
-            <v>0</v>
-          </cell>
-          <cell r="AW3">
-            <v>93.51</v>
-          </cell>
-          <cell r="AX3">
-            <v>0</v>
-          </cell>
-          <cell r="AY3">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="AR4">
-            <v>0</v>
-          </cell>
-          <cell r="AS4">
-            <v>0</v>
-          </cell>
-          <cell r="AT4">
-            <v>0</v>
-          </cell>
-          <cell r="AU4">
-            <v>0</v>
-          </cell>
-          <cell r="AV4">
-            <v>0</v>
-          </cell>
-          <cell r="AW4">
-            <v>0</v>
-          </cell>
-          <cell r="AX4">
-            <v>0</v>
-          </cell>
-          <cell r="AY4">
-            <v>100</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="AR5">
-            <v>1.29</v>
-          </cell>
-          <cell r="AS5">
-            <v>0</v>
-          </cell>
-          <cell r="AT5">
-            <v>0</v>
-          </cell>
-          <cell r="AU5">
-            <v>0</v>
-          </cell>
-          <cell r="AV5">
-            <v>0</v>
-          </cell>
-          <cell r="AW5">
-            <v>0</v>
-          </cell>
-          <cell r="AX5">
-            <v>0</v>
-          </cell>
-          <cell r="AY5">
-            <v>98.71</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
+  <oleLink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" progId="Excel.Sheet.12">
+    <oleItems>
+      <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+        <mc:Choice Requires="x14">
+          <x14:oleItem name="!results!L3C37:L3C40" advise="1">
+            <x14:values cols="4">
+              <value>
+                <val>2.66</val>
+              </value>
+              <value>
+                <val>1.06</val>
+              </value>
+              <value>
+                <val>18.36</val>
+              </value>
+              <value>
+                <val>77.930000000000007</val>
+              </value>
+            </x14:values>
+          </x14:oleItem>
+        </mc:Choice>
+        <mc:Fallback>
+          <oleItem name="!results!L3C37:L3C40" advise="1"/>
+        </mc:Fallback>
+      </mc:AlternateContent>
+      <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+        <mc:Choice Requires="x14">
+          <x14:oleItem name="!results!L4C37:L4C40" advise="1">
+            <x14:values cols="4">
+              <value>
+                <val>0</val>
+              </value>
+              <value>
+                <val>0</val>
+              </value>
+              <value>
+                <val>93.51</val>
+              </value>
+              <value>
+                <val>6.49</val>
+              </value>
+            </x14:values>
+          </x14:oleItem>
+        </mc:Choice>
+        <mc:Fallback>
+          <oleItem name="!results!L4C37:L4C40" advise="1"/>
+        </mc:Fallback>
+      </mc:AlternateContent>
+      <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+        <mc:Choice Requires="x14">
+          <x14:oleItem name="!results!L5C37:L5C40" advise="1">
+            <x14:values cols="4">
+              <value>
+                <val>0</val>
+              </value>
+              <value>
+                <val>0</val>
+              </value>
+              <value>
+                <val>87.36</val>
+              </value>
+              <value>
+                <val>12.64</val>
+              </value>
+            </x14:values>
+          </x14:oleItem>
+        </mc:Choice>
+        <mc:Fallback>
+          <oleItem name="!results!L5C37:L5C40" advise="1"/>
+        </mc:Fallback>
+      </mc:AlternateContent>
+    </oleItems>
+  </oleLink>
 </externalLink>
 </file>
 
 <file path=xl/externalLinks/externalLink9.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="results"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="3">
-          <cell r="AR3">
-            <v>6.5</v>
-          </cell>
-          <cell r="AS3">
-            <v>0</v>
-          </cell>
-          <cell r="AT3">
-            <v>0</v>
-          </cell>
-          <cell r="AU3">
-            <v>0</v>
-          </cell>
-          <cell r="AV3">
-            <v>0</v>
-          </cell>
-          <cell r="AW3">
-            <v>93.51</v>
-          </cell>
-          <cell r="AX3">
-            <v>0</v>
-          </cell>
-          <cell r="AY3">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="AR4">
-            <v>0</v>
-          </cell>
-          <cell r="AS4">
-            <v>0</v>
-          </cell>
-          <cell r="AT4">
-            <v>0</v>
-          </cell>
-          <cell r="AU4">
-            <v>0</v>
-          </cell>
-          <cell r="AV4">
-            <v>0</v>
-          </cell>
-          <cell r="AW4">
-            <v>0</v>
-          </cell>
-          <cell r="AX4">
-            <v>0</v>
-          </cell>
-          <cell r="AY4">
-            <v>100</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="AR5">
-            <v>1.29</v>
-          </cell>
-          <cell r="AS5">
-            <v>0</v>
-          </cell>
-          <cell r="AT5">
-            <v>0</v>
-          </cell>
-          <cell r="AU5">
-            <v>0</v>
-          </cell>
-          <cell r="AV5">
-            <v>0</v>
-          </cell>
-          <cell r="AW5">
-            <v>0</v>
-          </cell>
-          <cell r="AX5">
-            <v>0</v>
-          </cell>
-          <cell r="AY5">
-            <v>98.71</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
+  <oleLink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" progId="Excel.Sheet.12">
+    <oleItems>
+      <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+        <mc:Choice Requires="x14">
+          <x14:oleItem name="!results!L3C37:L3C40" advise="1">
+            <x14:values cols="4">
+              <value>
+                <val>23.900000000000002</val>
+              </value>
+              <value>
+                <val>29</val>
+              </value>
+              <value>
+                <val>0</val>
+              </value>
+              <value>
+                <val>47.11</val>
+              </value>
+            </x14:values>
+          </x14:oleItem>
+        </mc:Choice>
+        <mc:Fallback>
+          <oleItem name="!results!L3C37:L3C40" advise="1"/>
+        </mc:Fallback>
+      </mc:AlternateContent>
+      <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+        <mc:Choice Requires="x14">
+          <x14:oleItem name="!results!L4C37:L4C40" advise="1">
+            <x14:values cols="4">
+              <value>
+                <val>23.900000000000002</val>
+              </value>
+              <value>
+                <val>0</val>
+              </value>
+              <value>
+                <val>76.11</val>
+              </value>
+              <value>
+                <val>0</val>
+              </value>
+            </x14:values>
+          </x14:oleItem>
+        </mc:Choice>
+        <mc:Fallback>
+          <oleItem name="!results!L4C37:L4C40" advise="1"/>
+        </mc:Fallback>
+      </mc:AlternateContent>
+      <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+        <mc:Choice Requires="x14">
+          <x14:oleItem name="!results!L5C37:L5C40" advise="1">
+            <x14:values cols="4">
+              <value>
+                <val>23.900000000000002</val>
+              </value>
+              <value>
+                <val>0</val>
+              </value>
+              <value>
+                <val>76.11</val>
+              </value>
+              <value>
+                <val>0</val>
+              </value>
+            </x14:values>
+          </x14:oleItem>
+        </mc:Choice>
+        <mc:Fallback>
+          <oleItem name="!results!L5C37:L5C40" advise="1"/>
+        </mc:Fallback>
+      </mc:AlternateContent>
+    </oleItems>
+  </oleLink>
 </externalLink>
 </file>
 
@@ -3906,39 +4000,39 @@
         <v>-0.5</v>
       </c>
       <c r="C4">
-        <f>Q5</f>
-        <v>6.5</v>
+        <f t="shared" ref="C4:J4" si="0">Q5</f>
+        <v>0</v>
       </c>
       <c r="D4">
-        <f>R5</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E4">
-        <f>S5</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F4">
-        <f>T5</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G4">
-        <f>U5</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H4">
-        <f>V5</f>
-        <v>93.51</v>
+        <f t="shared" si="0"/>
+        <v>100</v>
       </c>
       <c r="I4">
-        <f>W5</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J4">
-        <f>X5</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="M4">
-        <f t="shared" ref="M4" si="0">Y5</f>
+        <f t="shared" ref="M4" si="1">Y5</f>
         <v>100.00999999999999</v>
       </c>
     </row>
@@ -3948,35 +4042,35 @@
         <v>minCC</v>
       </c>
       <c r="C5">
-        <f>[7]results!AR3</f>
+        <f>[4]results!AR3</f>
         <v>6.5</v>
       </c>
       <c r="D5">
-        <f>[7]results!AS3</f>
+        <f>[4]results!AS3</f>
         <v>0</v>
       </c>
       <c r="E5">
-        <f>[7]results!AT3</f>
+        <f>[4]results!AT3</f>
         <v>0</v>
       </c>
       <c r="F5">
-        <f>[7]results!AU3</f>
+        <f>[4]results!AU3</f>
         <v>0</v>
       </c>
       <c r="G5">
-        <f>[7]results!AV3</f>
+        <f>[4]results!AV3</f>
         <v>0</v>
       </c>
       <c r="H5">
-        <f>[7]results!AW3</f>
+        <f>[4]results!AW3</f>
         <v>93.51</v>
       </c>
       <c r="I5">
-        <f>[7]results!AX3</f>
+        <f>[4]results!AX3</f>
         <v>0</v>
       </c>
       <c r="J5">
-        <f>[7]results!AY3</f>
+        <f>[4]results!AY3</f>
         <v>0</v>
       </c>
       <c r="M5">
@@ -3988,35 +4082,28 @@
         <v>minCO2</v>
       </c>
       <c r="Q5">
-        <f>[9]results!AR3</f>
-        <v>6.5</v>
+        <f t="array" ref="Q5:X5">[10]!'!results!L3C44:L3C51'</f>
+        <v>0</v>
       </c>
       <c r="R5">
-        <f>[9]results!AS3</f>
         <v>0</v>
       </c>
       <c r="S5">
-        <f>[9]results!AT3</f>
         <v>0</v>
       </c>
       <c r="T5">
-        <f>[9]results!AU3</f>
         <v>0</v>
       </c>
       <c r="U5">
-        <f>[9]results!AV3</f>
         <v>0</v>
       </c>
       <c r="V5">
-        <f>[9]results!AW3</f>
-        <v>93.51</v>
+        <v>100</v>
       </c>
       <c r="W5">
-        <f>[9]results!AX3</f>
         <v>0</v>
       </c>
       <c r="X5">
-        <f>[9]results!AY3</f>
         <v>0</v>
       </c>
       <c r="Y5">
@@ -4028,35 +4115,28 @@
         <v>minCO2</v>
       </c>
       <c r="AB5">
-        <f>[8]results!AR3</f>
+        <f t="array" ref="AB5:AI5">[11]!'!results!L3C44:L3C51'</f>
         <v>6.5</v>
       </c>
       <c r="AC5">
-        <f>[8]results!AS3</f>
         <v>0</v>
       </c>
       <c r="AD5">
-        <f>[8]results!AT3</f>
         <v>0</v>
       </c>
       <c r="AE5">
-        <f>[8]results!AU3</f>
         <v>0</v>
       </c>
       <c r="AF5">
-        <f>[8]results!AV3</f>
         <v>0</v>
       </c>
       <c r="AG5">
-        <f>[8]results!AW3</f>
         <v>93.51</v>
       </c>
       <c r="AH5">
-        <f>[8]results!AX3</f>
         <v>0</v>
       </c>
       <c r="AI5">
-        <f>[8]results!AY3</f>
         <v>0</v>
       </c>
     </row>
@@ -4065,35 +4145,35 @@
         <v>0.5</v>
       </c>
       <c r="C6">
-        <f t="shared" ref="C6:J6" si="1">AB5</f>
+        <f t="shared" ref="C6:J6" si="2">AB5</f>
         <v>6.5</v>
       </c>
       <c r="D6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="E6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>93.51</v>
       </c>
       <c r="I6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -4102,39 +4182,39 @@
         <v>-0.5</v>
       </c>
       <c r="C8">
-        <f>Q9</f>
+        <f t="shared" ref="C8:J8" si="3">Q9</f>
         <v>0</v>
       </c>
       <c r="D8">
-        <f>R9</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="E8">
-        <f>S9</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="F8">
-        <f>T9</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G8">
-        <f>U9</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H8">
-        <f>V9</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I8">
-        <f>W9</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J8">
-        <f>X9</f>
+        <f t="shared" si="3"/>
         <v>100</v>
       </c>
       <c r="M8">
-        <f t="shared" ref="M8" si="2">Y9</f>
+        <f t="shared" ref="M8" si="4">Y9</f>
         <v>100.00999999999999</v>
       </c>
     </row>
@@ -4144,35 +4224,35 @@
         <v>minEQ</v>
       </c>
       <c r="C9">
-        <f>[7]results!AR4</f>
+        <f>[4]results!AR4</f>
         <v>0</v>
       </c>
       <c r="D9">
-        <f>[7]results!AS4</f>
+        <f>[4]results!AS4</f>
         <v>0</v>
       </c>
       <c r="E9">
-        <f>[7]results!AT4</f>
+        <f>[4]results!AT4</f>
         <v>0</v>
       </c>
       <c r="F9">
-        <f>[7]results!AU4</f>
+        <f>[4]results!AU4</f>
         <v>0</v>
       </c>
       <c r="G9">
-        <f>[7]results!AV4</f>
+        <f>[4]results!AV4</f>
         <v>0</v>
       </c>
       <c r="H9">
-        <f>[7]results!AW4</f>
+        <f>[4]results!AW4</f>
         <v>0</v>
       </c>
       <c r="I9">
-        <f>[7]results!AX4</f>
+        <f>[4]results!AX4</f>
         <v>0</v>
       </c>
       <c r="J9">
-        <f>[7]results!AY4</f>
+        <f>[4]results!AY4</f>
         <v>100</v>
       </c>
       <c r="M9">
@@ -4184,35 +4264,28 @@
         <v>minEQ</v>
       </c>
       <c r="Q9">
-        <f>[9]results!AR4</f>
+        <f t="array" ref="Q9:X9">[10]!'!results!L4C44:L4C51'</f>
         <v>0</v>
       </c>
       <c r="R9">
-        <f>[9]results!AS4</f>
         <v>0</v>
       </c>
       <c r="S9">
-        <f>[9]results!AT4</f>
         <v>0</v>
       </c>
       <c r="T9">
-        <f>[9]results!AU4</f>
         <v>0</v>
       </c>
       <c r="U9">
-        <f>[9]results!AV4</f>
         <v>0</v>
       </c>
       <c r="V9">
-        <f>[9]results!AW4</f>
         <v>0</v>
       </c>
       <c r="W9">
-        <f>[9]results!AX4</f>
         <v>0</v>
       </c>
       <c r="X9">
-        <f>[9]results!AY4</f>
         <v>100</v>
       </c>
       <c r="Y9">
@@ -4224,35 +4297,28 @@
         <v>minEQ</v>
       </c>
       <c r="AB9">
-        <f>[8]results!AR4</f>
+        <f t="array" ref="AB9:AI9">[11]!'!results!L4C44:L4C51'</f>
         <v>0</v>
       </c>
       <c r="AC9">
-        <f>[8]results!AS4</f>
         <v>0</v>
       </c>
       <c r="AD9">
-        <f>[8]results!AT4</f>
         <v>0</v>
       </c>
       <c r="AE9">
-        <f>[8]results!AU4</f>
         <v>0</v>
       </c>
       <c r="AF9">
-        <f>[8]results!AV4</f>
         <v>0</v>
       </c>
       <c r="AG9">
-        <f>[8]results!AW4</f>
         <v>0</v>
       </c>
       <c r="AH9">
-        <f>[8]results!AX4</f>
         <v>0</v>
       </c>
       <c r="AI9">
-        <f>[8]results!AY4</f>
         <v>100</v>
       </c>
     </row>
@@ -4261,35 +4327,35 @@
         <v>0.5</v>
       </c>
       <c r="C10">
-        <f t="shared" ref="C10:J10" si="3">AB9</f>
+        <f t="shared" ref="C10:J10" si="5">AB9</f>
         <v>0</v>
       </c>
       <c r="D10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="E10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="G10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="H10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="I10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="J10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>100</v>
       </c>
     </row>
@@ -4298,39 +4364,39 @@
         <v>-0.5</v>
       </c>
       <c r="C12">
-        <f>Q13</f>
-        <v>1.29</v>
+        <f t="shared" ref="C12:J12" si="6">Q13</f>
+        <v>0</v>
       </c>
       <c r="D12">
-        <f>R13</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E12">
-        <f>S13</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="F12">
-        <f>T13</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="G12">
-        <f>U13</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H12">
-        <f>V13</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="I12">
-        <f>W13</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="J12">
-        <f>X13</f>
-        <v>98.71</v>
+        <f t="shared" si="6"/>
+        <v>100</v>
       </c>
       <c r="M12">
-        <f t="shared" ref="M12" si="4">Y13</f>
+        <f t="shared" ref="M12" si="7">Y13</f>
         <v>100.00999999999999</v>
       </c>
     </row>
@@ -4340,35 +4406,35 @@
         <v>minHH</v>
       </c>
       <c r="C13">
-        <f>[7]results!AR5</f>
+        <f>[4]results!AR5</f>
         <v>1.29</v>
       </c>
       <c r="D13">
-        <f>[7]results!AS5</f>
+        <f>[4]results!AS5</f>
         <v>0</v>
       </c>
       <c r="E13">
-        <f>[7]results!AT5</f>
+        <f>[4]results!AT5</f>
         <v>0</v>
       </c>
       <c r="F13">
-        <f>[7]results!AU5</f>
+        <f>[4]results!AU5</f>
         <v>0</v>
       </c>
       <c r="G13">
-        <f>[7]results!AV5</f>
+        <f>[4]results!AV5</f>
         <v>0</v>
       </c>
       <c r="H13">
-        <f>[7]results!AW5</f>
+        <f>[4]results!AW5</f>
         <v>0</v>
       </c>
       <c r="I13">
-        <f>[7]results!AX5</f>
+        <f>[4]results!AX5</f>
         <v>0</v>
       </c>
       <c r="J13">
-        <f>[7]results!AY5</f>
+        <f>[4]results!AY5</f>
         <v>98.71</v>
       </c>
       <c r="M13">
@@ -4380,36 +4446,29 @@
         <v>minHH</v>
       </c>
       <c r="Q13">
-        <f>[9]results!AR5</f>
-        <v>1.29</v>
+        <f t="array" ref="Q13:X13">[10]!'!results!L5C44:L5C51'</f>
+        <v>0</v>
       </c>
       <c r="R13">
-        <f>[9]results!AS5</f>
         <v>0</v>
       </c>
       <c r="S13">
-        <f>[9]results!AT5</f>
         <v>0</v>
       </c>
       <c r="T13">
-        <f>[9]results!AU5</f>
         <v>0</v>
       </c>
       <c r="U13">
-        <f>[9]results!AV5</f>
         <v>0</v>
       </c>
       <c r="V13">
-        <f>[9]results!AW5</f>
         <v>0</v>
       </c>
       <c r="W13">
-        <f>[9]results!AX5</f>
         <v>0</v>
       </c>
       <c r="X13">
-        <f>[9]results!AY5</f>
-        <v>98.71</v>
+        <v>100</v>
       </c>
       <c r="Y13">
         <f>[2]results!AZ5</f>
@@ -4420,35 +4479,28 @@
         <v>minHH</v>
       </c>
       <c r="AB13">
-        <f>[8]results!AR5</f>
+        <f t="array" ref="AB13:AI13">[11]!'!results!L5C44:L5C51'</f>
         <v>1.29</v>
       </c>
       <c r="AC13">
-        <f>[8]results!AS5</f>
         <v>0</v>
       </c>
       <c r="AD13">
-        <f>[8]results!AT5</f>
         <v>0</v>
       </c>
       <c r="AE13">
-        <f>[8]results!AU5</f>
         <v>0</v>
       </c>
       <c r="AF13">
-        <f>[8]results!AV5</f>
         <v>0</v>
       </c>
       <c r="AG13">
-        <f>[8]results!AW5</f>
         <v>0</v>
       </c>
       <c r="AH13">
-        <f>[8]results!AX5</f>
         <v>0</v>
       </c>
       <c r="AI13">
-        <f>[8]results!AY5</f>
         <v>98.71</v>
       </c>
     </row>
@@ -4457,35 +4509,35 @@
         <v>0.5</v>
       </c>
       <c r="C14">
-        <f t="shared" ref="C14:J14" si="5">AB13</f>
+        <f t="shared" ref="C14:J14" si="8">AB13</f>
         <v>1.29</v>
       </c>
       <c r="D14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="E14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="F14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="G14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="H14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="I14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>98.71</v>
       </c>
     </row>
@@ -4516,166 +4568,160 @@
         <v>0</v>
       </c>
       <c r="B2" t="str">
-        <f>[4]results!AK2</f>
-        <v>HC</v>
-      </c>
-      <c r="C2" t="str">
-        <f>[4]results!AL2</f>
-        <v>IC</v>
-      </c>
-      <c r="D2" t="str">
-        <f>[4]results!AM2</f>
-        <v>AD-cog-comp</v>
-      </c>
-      <c r="E2" t="str">
-        <f>[4]results!AN2</f>
-        <v>AD-biomet-dig</v>
-      </c>
-      <c r="G2" t="str">
-        <f>[5]results!AJ2</f>
-        <v>name</v>
-      </c>
-      <c r="H2" t="str">
         <f>[5]results!AK2</f>
         <v>HC</v>
       </c>
-      <c r="I2" t="str">
+      <c r="C2" t="str">
         <f>[5]results!AL2</f>
         <v>IC</v>
       </c>
-      <c r="J2" t="str">
+      <c r="D2" t="str">
         <f>[5]results!AM2</f>
         <v>AD-cog-comp</v>
       </c>
-      <c r="K2" t="str">
+      <c r="E2" t="str">
         <f>[5]results!AN2</f>
         <v>AD-biomet-dig</v>
       </c>
-      <c r="L2">
-        <f>[5]results!AO2</f>
-        <v>0</v>
-      </c>
-      <c r="N2" t="str">
+      <c r="G2" t="str">
         <f>[6]results!AJ2</f>
         <v>name</v>
       </c>
-      <c r="O2" t="str">
+      <c r="H2" t="str">
         <f>[6]results!AK2</f>
         <v>HC</v>
       </c>
-      <c r="P2" t="str">
+      <c r="I2" t="str">
         <f>[6]results!AL2</f>
         <v>IC</v>
       </c>
-      <c r="Q2" t="str">
+      <c r="J2" t="str">
         <f>[6]results!AM2</f>
         <v>AD-cog-comp</v>
       </c>
-      <c r="R2" t="str">
+      <c r="K2" t="str">
         <f>[6]results!AN2</f>
         <v>AD-biomet-dig</v>
       </c>
+      <c r="L2">
+        <f>[6]results!AO2</f>
+        <v>0</v>
+      </c>
+      <c r="N2" t="str">
+        <f>[7]results!AJ2</f>
+        <v>name</v>
+      </c>
+      <c r="O2" t="str">
+        <f>[7]results!AK2</f>
+        <v>HC</v>
+      </c>
+      <c r="P2" t="str">
+        <f>[7]results!AL2</f>
+        <v>IC</v>
+      </c>
+      <c r="Q2" t="str">
+        <f>[7]results!AM2</f>
+        <v>AD-cog-comp</v>
+      </c>
+      <c r="R2" t="str">
+        <f>[7]results!AN2</f>
+        <v>AD-biomet-dig</v>
+      </c>
       <c r="S2">
-        <f>[6]results!AO2</f>
+        <f>[7]results!AO2</f>
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B3">
         <f>H4</f>
-        <v>11.95</v>
+        <v>2.66</v>
       </c>
       <c r="C3">
         <f>I4</f>
-        <v>14.5</v>
+        <v>1.06</v>
       </c>
       <c r="D3">
         <f>J4</f>
-        <v>0</v>
+        <v>18.36</v>
       </c>
       <c r="E3">
         <f>K4</f>
-        <v>73.55</v>
+        <v>77.930000000000007</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A4" t="str">
-        <f>[4]results!AJ3</f>
+        <f>[5]results!AJ3</f>
         <v>minCC</v>
       </c>
       <c r="B4">
-        <f>[4]results!AK3</f>
+        <f>[5]results!AK3</f>
         <v>13.280000000000001</v>
       </c>
       <c r="C4">
-        <f>[4]results!AL3</f>
+        <f>[5]results!AL3</f>
         <v>16.11</v>
       </c>
       <c r="D4">
-        <f>[4]results!AM3</f>
+        <f>[5]results!AM3</f>
         <v>0</v>
       </c>
       <c r="E4">
-        <f>[4]results!AN3</f>
+        <f>[5]results!AN3</f>
         <v>70.62</v>
       </c>
       <c r="G4" t="str">
-        <f>[5]results!AJ3</f>
-        <v>minCO2</v>
-      </c>
-      <c r="H4">
-        <f>[11]results!AK3</f>
-        <v>11.95</v>
-      </c>
-      <c r="I4">
-        <f>[11]results!AL3</f>
-        <v>14.5</v>
-      </c>
-      <c r="J4">
-        <f>[11]results!AM3</f>
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <f>[11]results!AN3</f>
-        <v>73.55</v>
-      </c>
-      <c r="L4">
-        <f>[5]results!AO3</f>
-        <v>100.00999999999999</v>
-      </c>
-      <c r="N4" t="str">
         <f>[6]results!AJ3</f>
         <v>minCO2</v>
       </c>
+      <c r="H4">
+        <f t="array" ref="H4:K4">[8]!'!results!L3C37:L3C40'</f>
+        <v>2.66</v>
+      </c>
+      <c r="I4">
+        <v>1.06</v>
+      </c>
+      <c r="J4">
+        <v>18.36</v>
+      </c>
+      <c r="K4">
+        <v>77.930000000000007</v>
+      </c>
+      <c r="L4">
+        <f>[6]results!AO3</f>
+        <v>100.00999999999999</v>
+      </c>
+      <c r="N4" t="str">
+        <f>[7]results!AJ3</f>
+        <v>minCO2</v>
+      </c>
       <c r="O4">
-        <f>[10]results!AK3</f>
-        <v>14.61</v>
+        <f t="array" ref="O4:R4">[9]!'!results!L3C37:L3C40'</f>
+        <v>23.900000000000002</v>
       </c>
       <c r="P4">
-        <f>[10]results!AL3</f>
-        <v>17.72</v>
+        <v>29</v>
       </c>
       <c r="Q4">
-        <f>[10]results!AM3</f>
         <v>0</v>
       </c>
       <c r="R4">
-        <f>[10]results!AN3</f>
-        <v>67.680000000000007</v>
+        <v>47.11</v>
       </c>
       <c r="S4">
-        <f>[6]results!AO3</f>
+        <f>[7]results!AO3</f>
         <v>100.01</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B5">
         <f>O4</f>
-        <v>14.61</v>
+        <v>23.900000000000002</v>
       </c>
       <c r="C5">
         <f>P4</f>
-        <v>17.72</v>
+        <v>29</v>
       </c>
       <c r="D5">
         <f>Q4</f>
@@ -4683,13 +4729,13 @@
       </c>
       <c r="E5">
         <f>R4</f>
-        <v>67.680000000000007</v>
+        <v>47.11</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B7">
         <f>H8</f>
-        <v>11.95</v>
+        <v>0</v>
       </c>
       <c r="C7">
         <f>I8</f>
@@ -4697,87 +4743,77 @@
       </c>
       <c r="D7">
         <f>J8</f>
-        <v>88.06</v>
+        <v>93.51</v>
       </c>
       <c r="E7">
         <f>K8</f>
-        <v>0</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A8" t="str">
-        <f>[4]results!AJ4</f>
-        <v>minEQ</v>
-      </c>
-      <c r="B8">
-        <f>[4]results!AK4</f>
-        <v>13.280000000000001</v>
-      </c>
-      <c r="C8">
-        <f>[4]results!AL4</f>
-        <v>0</v>
-      </c>
-      <c r="D8">
-        <f>[4]results!AM4</f>
-        <v>86.73</v>
-      </c>
-      <c r="E8">
-        <f>[4]results!AN4</f>
-        <v>0</v>
-      </c>
-      <c r="G8" t="str">
         <f>[5]results!AJ4</f>
         <v>minEQ</v>
       </c>
-      <c r="H8">
-        <f>[11]results!AK4</f>
-        <v>11.95</v>
-      </c>
-      <c r="I8">
-        <f>[11]results!AL4</f>
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <f>[11]results!AM4</f>
-        <v>88.06</v>
-      </c>
-      <c r="K8">
-        <f>[11]results!AN4</f>
-        <v>0</v>
-      </c>
-      <c r="L8">
-        <f>[5]results!AO4</f>
-        <v>100.00999999999999</v>
-      </c>
-      <c r="N8" t="str">
+      <c r="B8">
+        <f>[5]results!AK4</f>
+        <v>13.280000000000001</v>
+      </c>
+      <c r="C8">
+        <f>[5]results!AL4</f>
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <f>[5]results!AM4</f>
+        <v>86.73</v>
+      </c>
+      <c r="E8">
+        <f>[5]results!AN4</f>
+        <v>0</v>
+      </c>
+      <c r="G8" t="str">
         <f>[6]results!AJ4</f>
         <v>minEQ</v>
       </c>
+      <c r="H8">
+        <f t="array" ref="H8:K8">[8]!'!results!L4C37:L4C40'</f>
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>93.51</v>
+      </c>
+      <c r="K8">
+        <v>6.49</v>
+      </c>
+      <c r="N8" t="str">
+        <f>[7]results!AJ4</f>
+        <v>minEQ</v>
+      </c>
       <c r="O8">
-        <f>[10]results!AK4</f>
-        <v>14.61</v>
+        <f t="array" ref="O8:R8">[9]!'!results!L4C37:L4C40'</f>
+        <v>23.900000000000002</v>
       </c>
       <c r="P8">
-        <f>[10]results!AL4</f>
         <v>0</v>
       </c>
       <c r="Q8">
-        <f>[10]results!AM4</f>
-        <v>85.4</v>
+        <v>76.11</v>
       </c>
       <c r="R8">
-        <f>[10]results!AN4</f>
         <v>0</v>
       </c>
       <c r="S8">
-        <f>[6]results!AO4</f>
+        <f>[7]results!AO4</f>
         <v>100.00999999999999</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B9">
         <f>O8</f>
-        <v>14.61</v>
+        <v>23.900000000000002</v>
       </c>
       <c r="C9">
         <f>P8</f>
@@ -4785,7 +4821,7 @@
       </c>
       <c r="D9">
         <f>Q8</f>
-        <v>85.4</v>
+        <v>76.11</v>
       </c>
       <c r="E9">
         <f>R8</f>
@@ -4795,7 +4831,7 @@
     <row r="11" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B11">
         <f>H12</f>
-        <v>11.95</v>
+        <v>0</v>
       </c>
       <c r="C11">
         <f>I12</f>
@@ -4803,87 +4839,81 @@
       </c>
       <c r="D11">
         <f>J12</f>
-        <v>88.06</v>
+        <v>87.36</v>
       </c>
       <c r="E11">
         <f>K12</f>
-        <v>0</v>
+        <v>12.64</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A12" t="str">
-        <f>[4]results!AJ5</f>
-        <v>minHH</v>
-      </c>
-      <c r="B12">
-        <f>[4]results!AK5</f>
-        <v>13.280000000000001</v>
-      </c>
-      <c r="C12">
-        <f>[4]results!AL5</f>
-        <v>0</v>
-      </c>
-      <c r="D12">
-        <f>[4]results!AM5</f>
-        <v>86.73</v>
-      </c>
-      <c r="E12">
-        <f>[4]results!AN5</f>
-        <v>0</v>
-      </c>
-      <c r="G12" t="str">
         <f>[5]results!AJ5</f>
         <v>minHH</v>
       </c>
-      <c r="H12">
-        <f>[11]results!AK5</f>
-        <v>11.95</v>
-      </c>
-      <c r="I12">
-        <f>[11]results!AL5</f>
-        <v>0</v>
-      </c>
-      <c r="J12">
-        <f>[11]results!AM5</f>
-        <v>88.06</v>
-      </c>
-      <c r="K12">
-        <f>[11]results!AN5</f>
-        <v>0</v>
-      </c>
-      <c r="L12">
-        <f>[5]results!AO5</f>
-        <v>100.00999999999999</v>
-      </c>
-      <c r="N12" t="str">
+      <c r="B12">
+        <f>[5]results!AK5</f>
+        <v>13.280000000000001</v>
+      </c>
+      <c r="C12">
+        <f>[5]results!AL5</f>
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <f>[5]results!AM5</f>
+        <v>86.73</v>
+      </c>
+      <c r="E12">
+        <f>[5]results!AN5</f>
+        <v>0</v>
+      </c>
+      <c r="G12" t="str">
         <f>[6]results!AJ5</f>
         <v>minHH</v>
       </c>
+      <c r="H12">
+        <f t="array" ref="H12:K12">[8]!'!results!L5C37:L5C40'</f>
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>87.36</v>
+      </c>
+      <c r="K12">
+        <v>12.64</v>
+      </c>
+      <c r="L12">
+        <f>[6]results!AO5</f>
+        <v>100.00999999999999</v>
+      </c>
+      <c r="N12" t="str">
+        <f>[7]results!AJ5</f>
+        <v>minHH</v>
+      </c>
       <c r="O12">
-        <f>[10]results!AK5</f>
-        <v>14.61</v>
+        <f t="array" ref="O12:R12">[9]!'!results!L5C37:L5C40'</f>
+        <v>23.900000000000002</v>
       </c>
       <c r="P12">
-        <f>[10]results!AL5</f>
         <v>0</v>
       </c>
       <c r="Q12">
-        <f>[10]results!AM5</f>
-        <v>85.4</v>
+        <v>76.11</v>
       </c>
       <c r="R12">
-        <f>[10]results!AN5</f>
         <v>0</v>
       </c>
       <c r="S12">
-        <f>[6]results!AO5</f>
+        <f>[7]results!AO5</f>
         <v>100.00999999999999</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.35">
       <c r="B13">
         <f>O12</f>
-        <v>14.61</v>
+        <v>23.900000000000002</v>
       </c>
       <c r="C13">
         <f>P12</f>
@@ -4891,7 +4921,7 @@
       </c>
       <c r="D13">
         <f>Q12</f>
-        <v>85.4</v>
+        <v>76.11</v>
       </c>
       <c r="E13">
         <f>R12</f>

--- a/simulations/correction_peat_market/AS_marché/AS_marché_hobby/AS_resume_hobby.xlsx
+++ b/simulations/correction_peat_market/AS_marché/AS_marché_hobby/AS_resume_hobby.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\hravoaha\Desktop\Thèse\Thèse 2023\Objectif 2\biowaste_optim\simulations\correction_peat_market\AS_marché\AS_marché_hobby\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10CE4149-8174-44FF-A7E8-E6BA919836AA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19E3C3A4-7AFB-4A99-B031-EED2DA795BFE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2798,43 +2798,31 @@
     <oleItems>
       <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
         <mc:Choice Requires="x14">
-          <x14:oleItem name="!results!L3C44:L3C51" advise="1">
-            <x14:values cols="8">
-              <value>
-                <val>0</val>
-              </value>
-              <value>
-                <val>0</val>
-              </value>
-              <value>
-                <val>0</val>
-              </value>
-              <value>
-                <val>0</val>
-              </value>
-              <value>
-                <val>0</val>
-              </value>
-              <value>
-                <val>100</val>
-              </value>
-              <value>
-                <val>0</val>
-              </value>
-              <value>
-                <val>0</val>
+          <x14:oleItem name="!results!L3C37:L3C40" advise="1">
+            <x14:values cols="4">
+              <value>
+                <val>2.66</val>
+              </value>
+              <value>
+                <val>1.06</val>
+              </value>
+              <value>
+                <val>18.36</val>
+              </value>
+              <value>
+                <val>77.930000000000007</val>
               </value>
             </x14:values>
           </x14:oleItem>
         </mc:Choice>
         <mc:Fallback>
-          <oleItem name="!results!L3C44:L3C51" advise="1"/>
+          <oleItem name="!results!L3C37:L3C40" advise="1"/>
         </mc:Fallback>
       </mc:AlternateContent>
       <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
         <mc:Choice Requires="x14">
-          <x14:oleItem name="!results!L4C44:L4C51" advise="1">
-            <x14:values cols="8">
+          <x14:oleItem name="!results!L4C37:L4C40" advise="1">
+            <x14:values cols="4">
               <value>
                 <val>0</val>
               </value>
@@ -2842,34 +2830,22 @@
                 <val>0</val>
               </value>
               <value>
-                <val>0</val>
-              </value>
-              <value>
-                <val>0</val>
-              </value>
-              <value>
-                <val>0</val>
-              </value>
-              <value>
-                <val>0</val>
-              </value>
-              <value>
-                <val>0</val>
-              </value>
-              <value>
-                <val>100</val>
+                <val>93.51</val>
+              </value>
+              <value>
+                <val>6.49</val>
               </value>
             </x14:values>
           </x14:oleItem>
         </mc:Choice>
         <mc:Fallback>
-          <oleItem name="!results!L4C44:L4C51" advise="1"/>
+          <oleItem name="!results!L4C37:L4C40" advise="1"/>
         </mc:Fallback>
       </mc:AlternateContent>
       <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
         <mc:Choice Requires="x14">
-          <x14:oleItem name="!results!L5C44:L5C51" advise="1">
-            <x14:values cols="8">
+          <x14:oleItem name="!results!L5C37:L5C40" advise="1">
+            <x14:values cols="4">
               <value>
                 <val>0</val>
               </value>
@@ -2877,28 +2853,16 @@
                 <val>0</val>
               </value>
               <value>
-                <val>0</val>
-              </value>
-              <value>
-                <val>0</val>
-              </value>
-              <value>
-                <val>0</val>
-              </value>
-              <value>
-                <val>0</val>
-              </value>
-              <value>
-                <val>0</val>
-              </value>
-              <value>
-                <val>100</val>
+                <val>87.36</val>
+              </value>
+              <value>
+                <val>12.64</val>
               </value>
             </x14:values>
           </x14:oleItem>
         </mc:Choice>
         <mc:Fallback>
-          <oleItem name="!results!L5C44:L5C51" advise="1"/>
+          <oleItem name="!results!L5C37:L5C40" advise="1"/>
         </mc:Fallback>
       </mc:AlternateContent>
     </oleItems>
@@ -2912,107 +2876,71 @@
     <oleItems>
       <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
         <mc:Choice Requires="x14">
-          <x14:oleItem name="!results!L3C44:L3C51" advise="1">
-            <x14:values cols="8">
-              <value>
-                <val>6.5</val>
+          <x14:oleItem name="!results!L3C37:L3C40" advise="1">
+            <x14:values cols="4">
+              <value>
+                <val>23.900000000000002</val>
+              </value>
+              <value>
+                <val>29</val>
               </value>
               <value>
                 <val>0</val>
               </value>
               <value>
-                <val>0</val>
-              </value>
-              <value>
-                <val>0</val>
-              </value>
-              <value>
-                <val>0</val>
-              </value>
-              <value>
-                <val>93.51</val>
-              </value>
-              <value>
-                <val>0</val>
-              </value>
-              <value>
-                <val>0</val>
+                <val>47.11</val>
               </value>
             </x14:values>
           </x14:oleItem>
         </mc:Choice>
         <mc:Fallback>
-          <oleItem name="!results!L3C44:L3C51" advise="1"/>
+          <oleItem name="!results!L3C37:L3C40" advise="1"/>
         </mc:Fallback>
       </mc:AlternateContent>
       <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
         <mc:Choice Requires="x14">
-          <x14:oleItem name="!results!L4C44:L4C51" advise="1">
-            <x14:values cols="8">
+          <x14:oleItem name="!results!L4C37:L4C40" advise="1">
+            <x14:values cols="4">
+              <value>
+                <val>23.900000000000002</val>
+              </value>
               <value>
                 <val>0</val>
               </value>
               <value>
+                <val>76.11</val>
+              </value>
+              <value>
                 <val>0</val>
-              </value>
-              <value>
-                <val>0</val>
-              </value>
-              <value>
-                <val>0</val>
-              </value>
-              <value>
-                <val>0</val>
-              </value>
-              <value>
-                <val>0</val>
-              </value>
-              <value>
-                <val>0</val>
-              </value>
-              <value>
-                <val>100</val>
               </value>
             </x14:values>
           </x14:oleItem>
         </mc:Choice>
         <mc:Fallback>
-          <oleItem name="!results!L4C44:L4C51" advise="1"/>
+          <oleItem name="!results!L4C37:L4C40" advise="1"/>
         </mc:Fallback>
       </mc:AlternateContent>
       <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
         <mc:Choice Requires="x14">
-          <x14:oleItem name="!results!L5C44:L5C51" advise="1">
-            <x14:values cols="8">
-              <value>
-                <val>1.29</val>
+          <x14:oleItem name="!results!L5C37:L5C40" advise="1">
+            <x14:values cols="4">
+              <value>
+                <val>23.900000000000002</val>
               </value>
               <value>
                 <val>0</val>
               </value>
               <value>
+                <val>76.11</val>
+              </value>
+              <value>
                 <val>0</val>
-              </value>
-              <value>
-                <val>0</val>
-              </value>
-              <value>
-                <val>0</val>
-              </value>
-              <value>
-                <val>0</val>
-              </value>
-              <value>
-                <val>0</val>
-              </value>
-              <value>
-                <val>98.71</val>
               </value>
             </x14:values>
           </x14:oleItem>
         </mc:Choice>
         <mc:Fallback>
-          <oleItem name="!results!L5C44:L5C51" advise="1"/>
+          <oleItem name="!results!L5C37:L5C40" advise="1"/>
         </mc:Fallback>
       </mc:AlternateContent>
     </oleItems>
@@ -3242,6 +3170,234 @@
 
 <file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <oleLink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" progId="Excel.Sheet.12">
+    <oleItems>
+      <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+        <mc:Choice Requires="x14">
+          <x14:oleItem name="!results!L3C44:L3C51" advise="1">
+            <x14:values cols="8">
+              <value>
+                <val>0</val>
+              </value>
+              <value>
+                <val>0</val>
+              </value>
+              <value>
+                <val>0</val>
+              </value>
+              <value>
+                <val>0</val>
+              </value>
+              <value>
+                <val>0</val>
+              </value>
+              <value>
+                <val>100</val>
+              </value>
+              <value>
+                <val>0</val>
+              </value>
+              <value>
+                <val>0</val>
+              </value>
+            </x14:values>
+          </x14:oleItem>
+        </mc:Choice>
+        <mc:Fallback>
+          <oleItem name="!results!L3C44:L3C51" advise="1"/>
+        </mc:Fallback>
+      </mc:AlternateContent>
+      <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+        <mc:Choice Requires="x14">
+          <x14:oleItem name="!results!L4C44:L4C51" advise="1">
+            <x14:values cols="8">
+              <value>
+                <val>0</val>
+              </value>
+              <value>
+                <val>0</val>
+              </value>
+              <value>
+                <val>0</val>
+              </value>
+              <value>
+                <val>0</val>
+              </value>
+              <value>
+                <val>0</val>
+              </value>
+              <value>
+                <val>0</val>
+              </value>
+              <value>
+                <val>0</val>
+              </value>
+              <value>
+                <val>100</val>
+              </value>
+            </x14:values>
+          </x14:oleItem>
+        </mc:Choice>
+        <mc:Fallback>
+          <oleItem name="!results!L4C44:L4C51" advise="1"/>
+        </mc:Fallback>
+      </mc:AlternateContent>
+      <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+        <mc:Choice Requires="x14">
+          <x14:oleItem name="!results!L5C44:L5C51" advise="1">
+            <x14:values cols="8">
+              <value>
+                <val>0</val>
+              </value>
+              <value>
+                <val>0</val>
+              </value>
+              <value>
+                <val>0</val>
+              </value>
+              <value>
+                <val>0</val>
+              </value>
+              <value>
+                <val>0</val>
+              </value>
+              <value>
+                <val>0</val>
+              </value>
+              <value>
+                <val>0</val>
+              </value>
+              <value>
+                <val>100</val>
+              </value>
+            </x14:values>
+          </x14:oleItem>
+        </mc:Choice>
+        <mc:Fallback>
+          <oleItem name="!results!L5C44:L5C51" advise="1"/>
+        </mc:Fallback>
+      </mc:AlternateContent>
+    </oleItems>
+  </oleLink>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <oleLink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" progId="Excel.Sheet.12">
+    <oleItems>
+      <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+        <mc:Choice Requires="x14">
+          <x14:oleItem name="!results!L3C44:L3C51" advise="1">
+            <x14:values cols="8">
+              <value>
+                <val>6.5</val>
+              </value>
+              <value>
+                <val>0</val>
+              </value>
+              <value>
+                <val>0</val>
+              </value>
+              <value>
+                <val>0</val>
+              </value>
+              <value>
+                <val>0</val>
+              </value>
+              <value>
+                <val>93.51</val>
+              </value>
+              <value>
+                <val>0</val>
+              </value>
+              <value>
+                <val>0</val>
+              </value>
+            </x14:values>
+          </x14:oleItem>
+        </mc:Choice>
+        <mc:Fallback>
+          <oleItem name="!results!L3C44:L3C51" advise="1"/>
+        </mc:Fallback>
+      </mc:AlternateContent>
+      <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+        <mc:Choice Requires="x14">
+          <x14:oleItem name="!results!L4C44:L4C51" advise="1">
+            <x14:values cols="8">
+              <value>
+                <val>0</val>
+              </value>
+              <value>
+                <val>0</val>
+              </value>
+              <value>
+                <val>0</val>
+              </value>
+              <value>
+                <val>0</val>
+              </value>
+              <value>
+                <val>0</val>
+              </value>
+              <value>
+                <val>0</val>
+              </value>
+              <value>
+                <val>0</val>
+              </value>
+              <value>
+                <val>100</val>
+              </value>
+            </x14:values>
+          </x14:oleItem>
+        </mc:Choice>
+        <mc:Fallback>
+          <oleItem name="!results!L4C44:L4C51" advise="1"/>
+        </mc:Fallback>
+      </mc:AlternateContent>
+      <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+        <mc:Choice Requires="x14">
+          <x14:oleItem name="!results!L5C44:L5C51" advise="1">
+            <x14:values cols="8">
+              <value>
+                <val>1.29</val>
+              </value>
+              <value>
+                <val>0</val>
+              </value>
+              <value>
+                <val>0</val>
+              </value>
+              <value>
+                <val>0</val>
+              </value>
+              <value>
+                <val>0</val>
+              </value>
+              <value>
+                <val>0</val>
+              </value>
+              <value>
+                <val>0</val>
+              </value>
+              <value>
+                <val>98.71</val>
+              </value>
+            </x14:values>
+          </x14:oleItem>
+        </mc:Choice>
+        <mc:Fallback>
+          <oleItem name="!results!L5C44:L5C51" advise="1"/>
+        </mc:Fallback>
+      </mc:AlternateContent>
+    </oleItems>
+  </oleLink>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink7.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Contrainte de capacité"/>
@@ -3331,7 +3487,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink8.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -3383,7 +3539,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink9.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -3435,162 +3591,6 @@
       </sheetData>
     </sheetDataSet>
   </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink8.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <oleLink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" progId="Excel.Sheet.12">
-    <oleItems>
-      <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-        <mc:Choice Requires="x14">
-          <x14:oleItem name="!results!L3C37:L3C40" advise="1">
-            <x14:values cols="4">
-              <value>
-                <val>2.66</val>
-              </value>
-              <value>
-                <val>1.06</val>
-              </value>
-              <value>
-                <val>18.36</val>
-              </value>
-              <value>
-                <val>77.930000000000007</val>
-              </value>
-            </x14:values>
-          </x14:oleItem>
-        </mc:Choice>
-        <mc:Fallback>
-          <oleItem name="!results!L3C37:L3C40" advise="1"/>
-        </mc:Fallback>
-      </mc:AlternateContent>
-      <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-        <mc:Choice Requires="x14">
-          <x14:oleItem name="!results!L4C37:L4C40" advise="1">
-            <x14:values cols="4">
-              <value>
-                <val>0</val>
-              </value>
-              <value>
-                <val>0</val>
-              </value>
-              <value>
-                <val>93.51</val>
-              </value>
-              <value>
-                <val>6.49</val>
-              </value>
-            </x14:values>
-          </x14:oleItem>
-        </mc:Choice>
-        <mc:Fallback>
-          <oleItem name="!results!L4C37:L4C40" advise="1"/>
-        </mc:Fallback>
-      </mc:AlternateContent>
-      <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-        <mc:Choice Requires="x14">
-          <x14:oleItem name="!results!L5C37:L5C40" advise="1">
-            <x14:values cols="4">
-              <value>
-                <val>0</val>
-              </value>
-              <value>
-                <val>0</val>
-              </value>
-              <value>
-                <val>87.36</val>
-              </value>
-              <value>
-                <val>12.64</val>
-              </value>
-            </x14:values>
-          </x14:oleItem>
-        </mc:Choice>
-        <mc:Fallback>
-          <oleItem name="!results!L5C37:L5C40" advise="1"/>
-        </mc:Fallback>
-      </mc:AlternateContent>
-    </oleItems>
-  </oleLink>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink9.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <oleLink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" progId="Excel.Sheet.12">
-    <oleItems>
-      <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-        <mc:Choice Requires="x14">
-          <x14:oleItem name="!results!L3C37:L3C40" advise="1">
-            <x14:values cols="4">
-              <value>
-                <val>23.900000000000002</val>
-              </value>
-              <value>
-                <val>29</val>
-              </value>
-              <value>
-                <val>0</val>
-              </value>
-              <value>
-                <val>47.11</val>
-              </value>
-            </x14:values>
-          </x14:oleItem>
-        </mc:Choice>
-        <mc:Fallback>
-          <oleItem name="!results!L3C37:L3C40" advise="1"/>
-        </mc:Fallback>
-      </mc:AlternateContent>
-      <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-        <mc:Choice Requires="x14">
-          <x14:oleItem name="!results!L4C37:L4C40" advise="1">
-            <x14:values cols="4">
-              <value>
-                <val>23.900000000000002</val>
-              </value>
-              <value>
-                <val>0</val>
-              </value>
-              <value>
-                <val>76.11</val>
-              </value>
-              <value>
-                <val>0</val>
-              </value>
-            </x14:values>
-          </x14:oleItem>
-        </mc:Choice>
-        <mc:Fallback>
-          <oleItem name="!results!L4C37:L4C40" advise="1"/>
-        </mc:Fallback>
-      </mc:AlternateContent>
-      <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-        <mc:Choice Requires="x14">
-          <x14:oleItem name="!results!L5C37:L5C40" advise="1">
-            <x14:values cols="4">
-              <value>
-                <val>23.900000000000002</val>
-              </value>
-              <value>
-                <val>0</val>
-              </value>
-              <value>
-                <val>76.11</val>
-              </value>
-              <value>
-                <val>0</val>
-              </value>
-            </x14:values>
-          </x14:oleItem>
-        </mc:Choice>
-        <mc:Fallback>
-          <oleItem name="!results!L5C37:L5C40" advise="1"/>
-        </mc:Fallback>
-      </mc:AlternateContent>
-    </oleItems>
-  </oleLink>
 </externalLink>
 </file>
 
@@ -4082,7 +4082,7 @@
         <v>minCO2</v>
       </c>
       <c r="Q5">
-        <f t="array" ref="Q5:X5">[10]!'!results!L3C44:L3C51'</f>
+        <f t="array" ref="Q5:X5">[5]!'!results!L3C44:L3C51'</f>
         <v>0</v>
       </c>
       <c r="R5">
@@ -4115,7 +4115,7 @@
         <v>minCO2</v>
       </c>
       <c r="AB5">
-        <f t="array" ref="AB5:AI5">[11]!'!results!L3C44:L3C51'</f>
+        <f t="array" ref="AB5:AI5">[6]!'!results!L3C44:L3C51'</f>
         <v>6.5</v>
       </c>
       <c r="AC5">
@@ -4264,7 +4264,7 @@
         <v>minEQ</v>
       </c>
       <c r="Q9">
-        <f t="array" ref="Q9:X9">[10]!'!results!L4C44:L4C51'</f>
+        <f t="array" ref="Q9:X9">[5]!'!results!L4C44:L4C51'</f>
         <v>0</v>
       </c>
       <c r="R9">
@@ -4297,7 +4297,7 @@
         <v>minEQ</v>
       </c>
       <c r="AB9">
-        <f t="array" ref="AB9:AI9">[11]!'!results!L4C44:L4C51'</f>
+        <f t="array" ref="AB9:AI9">[6]!'!results!L4C44:L4C51'</f>
         <v>0</v>
       </c>
       <c r="AC9">
@@ -4446,7 +4446,7 @@
         <v>minHH</v>
       </c>
       <c r="Q13">
-        <f t="array" ref="Q13:X13">[10]!'!results!L5C44:L5C51'</f>
+        <f t="array" ref="Q13:X13">[5]!'!results!L5C44:L5C51'</f>
         <v>0</v>
       </c>
       <c r="R13">
@@ -4479,7 +4479,7 @@
         <v>minHH</v>
       </c>
       <c r="AB13">
-        <f t="array" ref="AB13:AI13">[11]!'!results!L5C44:L5C51'</f>
+        <f t="array" ref="AB13:AI13">[6]!'!results!L5C44:L5C51'</f>
         <v>1.29</v>
       </c>
       <c r="AC13">
@@ -4568,67 +4568,67 @@
         <v>0</v>
       </c>
       <c r="B2" t="str">
-        <f>[5]results!AK2</f>
-        <v>HC</v>
-      </c>
-      <c r="C2" t="str">
-        <f>[5]results!AL2</f>
-        <v>IC</v>
-      </c>
-      <c r="D2" t="str">
-        <f>[5]results!AM2</f>
-        <v>AD-cog-comp</v>
-      </c>
-      <c r="E2" t="str">
-        <f>[5]results!AN2</f>
-        <v>AD-biomet-dig</v>
-      </c>
-      <c r="G2" t="str">
-        <f>[6]results!AJ2</f>
-        <v>name</v>
-      </c>
-      <c r="H2" t="str">
-        <f>[6]results!AK2</f>
-        <v>HC</v>
-      </c>
-      <c r="I2" t="str">
-        <f>[6]results!AL2</f>
-        <v>IC</v>
-      </c>
-      <c r="J2" t="str">
-        <f>[6]results!AM2</f>
-        <v>AD-cog-comp</v>
-      </c>
-      <c r="K2" t="str">
-        <f>[6]results!AN2</f>
-        <v>AD-biomet-dig</v>
-      </c>
-      <c r="L2">
-        <f>[6]results!AO2</f>
-        <v>0</v>
-      </c>
-      <c r="N2" t="str">
-        <f>[7]results!AJ2</f>
-        <v>name</v>
-      </c>
-      <c r="O2" t="str">
         <f>[7]results!AK2</f>
         <v>HC</v>
       </c>
-      <c r="P2" t="str">
+      <c r="C2" t="str">
         <f>[7]results!AL2</f>
         <v>IC</v>
       </c>
-      <c r="Q2" t="str">
+      <c r="D2" t="str">
         <f>[7]results!AM2</f>
         <v>AD-cog-comp</v>
       </c>
-      <c r="R2" t="str">
+      <c r="E2" t="str">
         <f>[7]results!AN2</f>
         <v>AD-biomet-dig</v>
       </c>
+      <c r="G2" t="str">
+        <f>[8]results!AJ2</f>
+        <v>name</v>
+      </c>
+      <c r="H2" t="str">
+        <f>[8]results!AK2</f>
+        <v>HC</v>
+      </c>
+      <c r="I2" t="str">
+        <f>[8]results!AL2</f>
+        <v>IC</v>
+      </c>
+      <c r="J2" t="str">
+        <f>[8]results!AM2</f>
+        <v>AD-cog-comp</v>
+      </c>
+      <c r="K2" t="str">
+        <f>[8]results!AN2</f>
+        <v>AD-biomet-dig</v>
+      </c>
+      <c r="L2">
+        <f>[8]results!AO2</f>
+        <v>0</v>
+      </c>
+      <c r="N2" t="str">
+        <f>[9]results!AJ2</f>
+        <v>name</v>
+      </c>
+      <c r="O2" t="str">
+        <f>[9]results!AK2</f>
+        <v>HC</v>
+      </c>
+      <c r="P2" t="str">
+        <f>[9]results!AL2</f>
+        <v>IC</v>
+      </c>
+      <c r="Q2" t="str">
+        <f>[9]results!AM2</f>
+        <v>AD-cog-comp</v>
+      </c>
+      <c r="R2" t="str">
+        <f>[9]results!AN2</f>
+        <v>AD-biomet-dig</v>
+      </c>
       <c r="S2">
-        <f>[7]results!AO2</f>
+        <f>[9]results!AO2</f>
         <v>0</v>
       </c>
     </row>
@@ -4652,31 +4652,31 @@
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A4" t="str">
-        <f>[5]results!AJ3</f>
+        <f>[7]results!AJ3</f>
         <v>minCC</v>
       </c>
       <c r="B4">
-        <f>[5]results!AK3</f>
+        <f>[7]results!AK3</f>
         <v>13.280000000000001</v>
       </c>
       <c r="C4">
-        <f>[5]results!AL3</f>
+        <f>[7]results!AL3</f>
         <v>16.11</v>
       </c>
       <c r="D4">
-        <f>[5]results!AM3</f>
+        <f>[7]results!AM3</f>
         <v>0</v>
       </c>
       <c r="E4">
-        <f>[5]results!AN3</f>
+        <f>[7]results!AN3</f>
         <v>70.62</v>
       </c>
       <c r="G4" t="str">
-        <f>[6]results!AJ3</f>
+        <f>[8]results!AJ3</f>
         <v>minCO2</v>
       </c>
       <c r="H4">
-        <f t="array" ref="H4:K4">[8]!'!results!L3C37:L3C40'</f>
+        <f t="array" ref="H4:K4">[10]!'!results!L3C37:L3C40'</f>
         <v>2.66</v>
       </c>
       <c r="I4">
@@ -4689,15 +4689,15 @@
         <v>77.930000000000007</v>
       </c>
       <c r="L4">
-        <f>[6]results!AO3</f>
+        <f>[8]results!AO3</f>
         <v>100.00999999999999</v>
       </c>
       <c r="N4" t="str">
-        <f>[7]results!AJ3</f>
+        <f>[9]results!AJ3</f>
         <v>minCO2</v>
       </c>
       <c r="O4">
-        <f t="array" ref="O4:R4">[9]!'!results!L3C37:L3C40'</f>
+        <f t="array" ref="O4:R4">[11]!'!results!L3C37:L3C40'</f>
         <v>23.900000000000002</v>
       </c>
       <c r="P4">
@@ -4710,7 +4710,7 @@
         <v>47.11</v>
       </c>
       <c r="S4">
-        <f>[7]results!AO3</f>
+        <f>[9]results!AO3</f>
         <v>100.01</v>
       </c>
     </row>
@@ -4752,31 +4752,31 @@
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A8" t="str">
-        <f>[5]results!AJ4</f>
+        <f>[7]results!AJ4</f>
         <v>minEQ</v>
       </c>
       <c r="B8">
-        <f>[5]results!AK4</f>
+        <f>[7]results!AK4</f>
         <v>13.280000000000001</v>
       </c>
       <c r="C8">
-        <f>[5]results!AL4</f>
+        <f>[7]results!AL4</f>
         <v>0</v>
       </c>
       <c r="D8">
-        <f>[5]results!AM4</f>
+        <f>[7]results!AM4</f>
         <v>86.73</v>
       </c>
       <c r="E8">
-        <f>[5]results!AN4</f>
+        <f>[7]results!AN4</f>
         <v>0</v>
       </c>
       <c r="G8" t="str">
-        <f>[6]results!AJ4</f>
+        <f>[8]results!AJ4</f>
         <v>minEQ</v>
       </c>
       <c r="H8">
-        <f t="array" ref="H8:K8">[8]!'!results!L4C37:L4C40'</f>
+        <f t="array" ref="H8:K8">[10]!'!results!L4C37:L4C40'</f>
         <v>0</v>
       </c>
       <c r="I8">
@@ -4789,11 +4789,11 @@
         <v>6.49</v>
       </c>
       <c r="N8" t="str">
-        <f>[7]results!AJ4</f>
+        <f>[9]results!AJ4</f>
         <v>minEQ</v>
       </c>
       <c r="O8">
-        <f t="array" ref="O8:R8">[9]!'!results!L4C37:L4C40'</f>
+        <f t="array" ref="O8:R8">[11]!'!results!L4C37:L4C40'</f>
         <v>23.900000000000002</v>
       </c>
       <c r="P8">
@@ -4806,7 +4806,7 @@
         <v>0</v>
       </c>
       <c r="S8">
-        <f>[7]results!AO4</f>
+        <f>[9]results!AO4</f>
         <v>100.00999999999999</v>
       </c>
     </row>
@@ -4848,31 +4848,31 @@
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A12" t="str">
-        <f>[5]results!AJ5</f>
+        <f>[7]results!AJ5</f>
         <v>minHH</v>
       </c>
       <c r="B12">
-        <f>[5]results!AK5</f>
+        <f>[7]results!AK5</f>
         <v>13.280000000000001</v>
       </c>
       <c r="C12">
-        <f>[5]results!AL5</f>
+        <f>[7]results!AL5</f>
         <v>0</v>
       </c>
       <c r="D12">
-        <f>[5]results!AM5</f>
+        <f>[7]results!AM5</f>
         <v>86.73</v>
       </c>
       <c r="E12">
-        <f>[5]results!AN5</f>
+        <f>[7]results!AN5</f>
         <v>0</v>
       </c>
       <c r="G12" t="str">
-        <f>[6]results!AJ5</f>
+        <f>[8]results!AJ5</f>
         <v>minHH</v>
       </c>
       <c r="H12">
-        <f t="array" ref="H12:K12">[8]!'!results!L5C37:L5C40'</f>
+        <f t="array" ref="H12:K12">[10]!'!results!L5C37:L5C40'</f>
         <v>0</v>
       </c>
       <c r="I12">
@@ -4885,15 +4885,15 @@
         <v>12.64</v>
       </c>
       <c r="L12">
-        <f>[6]results!AO5</f>
+        <f>[8]results!AO5</f>
         <v>100.00999999999999</v>
       </c>
       <c r="N12" t="str">
-        <f>[7]results!AJ5</f>
+        <f>[9]results!AJ5</f>
         <v>minHH</v>
       </c>
       <c r="O12">
-        <f t="array" ref="O12:R12">[9]!'!results!L5C37:L5C40'</f>
+        <f t="array" ref="O12:R12">[11]!'!results!L5C37:L5C40'</f>
         <v>23.900000000000002</v>
       </c>
       <c r="P12">
@@ -4906,7 +4906,7 @@
         <v>0</v>
       </c>
       <c r="S12">
-        <f>[7]results!AO5</f>
+        <f>[9]results!AO5</f>
         <v>100.00999999999999</v>
       </c>
     </row>
